--- a/artfynd/A 28104-2026 artfynd.xlsx
+++ b/artfynd/A 28104-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135593890</v>
       </c>
       <c r="B2" t="n">
-        <v>91970</v>
+        <v>92012</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135593864</v>
       </c>
       <c r="B3" t="n">
-        <v>83222</v>
+        <v>83262</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135593858</v>
       </c>
       <c r="B4" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135593866</v>
       </c>
       <c r="B5" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135593883</v>
       </c>
       <c r="B6" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1248,7 +1248,7 @@
         <v>135593884</v>
       </c>
       <c r="B7" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         <v>135593885</v>
       </c>
       <c r="B8" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>135593886</v>
       </c>
       <c r="B9" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
         <v>135593895</v>
       </c>
       <c r="B10" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1701,7 +1701,7 @@
         <v>135593863</v>
       </c>
       <c r="B11" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1813,7 +1813,7 @@
         <v>135593871</v>
       </c>
       <c r="B12" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1925,7 +1925,7 @@
         <v>135593881</v>
       </c>
       <c r="B13" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2037,7 +2037,7 @@
         <v>135593889</v>
       </c>
       <c r="B14" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
         <v>135593875</v>
       </c>
       <c r="B15" t="n">
-        <v>57972</v>
+        <v>57977</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2266,7 +2266,7 @@
         <v>135593860</v>
       </c>
       <c r="B16" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2383,7 +2383,7 @@
         <v>135593861</v>
       </c>
       <c r="B17" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2500,7 +2500,7 @@
         <v>135593877</v>
       </c>
       <c r="B18" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2617,7 +2617,7 @@
         <v>135593878</v>
       </c>
       <c r="B19" t="n">
-        <v>58136</v>
+        <v>58141</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2745,7 +2745,7 @@
         <v>135593882</v>
       </c>
       <c r="B20" t="n">
-        <v>58136</v>
+        <v>58141</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2873,7 +2873,7 @@
         <v>135593865</v>
       </c>
       <c r="B21" t="n">
-        <v>99112</v>
+        <v>99159</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2985,7 +2985,7 @@
         <v>135593892</v>
       </c>
       <c r="B22" t="n">
-        <v>99112</v>
+        <v>99159</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3097,7 +3097,7 @@
         <v>135593867</v>
       </c>
       <c r="B23" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3214,7 +3214,7 @@
         <v>135593868</v>
       </c>
       <c r="B24" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3331,7 +3331,7 @@
         <v>135593869</v>
       </c>
       <c r="B25" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3448,7 +3448,7 @@
         <v>135593872</v>
       </c>
       <c r="B26" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3565,7 +3565,7 @@
         <v>135593873</v>
       </c>
       <c r="B27" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3682,7 +3682,7 @@
         <v>135593874</v>
       </c>
       <c r="B28" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3799,7 +3799,7 @@
         <v>135593887</v>
       </c>
       <c r="B29" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3921,7 +3921,7 @@
         <v>135593891</v>
       </c>
       <c r="B30" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4038,7 +4038,7 @@
         <v>135593893</v>
       </c>
       <c r="B31" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4155,7 +4155,7 @@
         <v>135593894</v>
       </c>
       <c r="B32" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4272,7 +4272,7 @@
         <v>135593896</v>
       </c>
       <c r="B33" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4389,7 +4389,7 @@
         <v>135593859</v>
       </c>
       <c r="B34" t="n">
-        <v>78382</v>
+        <v>78420</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4501,7 +4501,7 @@
         <v>135593862</v>
       </c>
       <c r="B35" t="n">
-        <v>78382</v>
+        <v>78420</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4613,7 +4613,7 @@
         <v>135593870</v>
       </c>
       <c r="B36" t="n">
-        <v>78382</v>
+        <v>78420</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4725,7 +4725,7 @@
         <v>135593880</v>
       </c>
       <c r="B37" t="n">
-        <v>78382</v>
+        <v>78420</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 28104-2026 artfynd.xlsx
+++ b/artfynd/A 28104-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135593890</v>
       </c>
       <c r="B2" t="n">
-        <v>92012</v>
+        <v>92039</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135593864</v>
       </c>
       <c r="B3" t="n">
-        <v>83262</v>
+        <v>83289</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135593858</v>
       </c>
       <c r="B4" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135593866</v>
       </c>
       <c r="B5" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135593883</v>
       </c>
       <c r="B6" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1248,7 +1248,7 @@
         <v>135593884</v>
       </c>
       <c r="B7" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         <v>135593885</v>
       </c>
       <c r="B8" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>135593886</v>
       </c>
       <c r="B9" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
         <v>135593895</v>
       </c>
       <c r="B10" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1701,7 +1701,7 @@
         <v>135593863</v>
       </c>
       <c r="B11" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1813,7 +1813,7 @@
         <v>135593871</v>
       </c>
       <c r="B12" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1925,7 +1925,7 @@
         <v>135593881</v>
       </c>
       <c r="B13" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2037,7 +2037,7 @@
         <v>135593889</v>
       </c>
       <c r="B14" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2873,7 +2873,7 @@
         <v>135593865</v>
       </c>
       <c r="B21" t="n">
-        <v>99159</v>
+        <v>99186</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2985,7 +2985,7 @@
         <v>135593892</v>
       </c>
       <c r="B22" t="n">
-        <v>99159</v>
+        <v>99186</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3097,7 +3097,7 @@
         <v>135593867</v>
       </c>
       <c r="B23" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3214,7 +3214,7 @@
         <v>135593868</v>
       </c>
       <c r="B24" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3331,7 +3331,7 @@
         <v>135593869</v>
       </c>
       <c r="B25" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3448,7 +3448,7 @@
         <v>135593872</v>
       </c>
       <c r="B26" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3565,7 +3565,7 @@
         <v>135593873</v>
       </c>
       <c r="B27" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3682,7 +3682,7 @@
         <v>135593874</v>
       </c>
       <c r="B28" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3799,7 +3799,7 @@
         <v>135593887</v>
       </c>
       <c r="B29" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3921,7 +3921,7 @@
         <v>135593891</v>
       </c>
       <c r="B30" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4038,7 +4038,7 @@
         <v>135593893</v>
       </c>
       <c r="B31" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4155,7 +4155,7 @@
         <v>135593894</v>
       </c>
       <c r="B32" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4272,7 +4272,7 @@
         <v>135593896</v>
       </c>
       <c r="B33" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4389,7 +4389,7 @@
         <v>135593859</v>
       </c>
       <c r="B34" t="n">
-        <v>78420</v>
+        <v>78447</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4501,7 +4501,7 @@
         <v>135593862</v>
       </c>
       <c r="B35" t="n">
-        <v>78420</v>
+        <v>78447</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4613,7 +4613,7 @@
         <v>135593870</v>
       </c>
       <c r="B36" t="n">
-        <v>78420</v>
+        <v>78447</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4725,7 +4725,7 @@
         <v>135593880</v>
       </c>
       <c r="B37" t="n">
-        <v>78420</v>
+        <v>78447</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 28104-2026 artfynd.xlsx
+++ b/artfynd/A 28104-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135593890</v>
       </c>
       <c r="B2" t="n">
-        <v>92044</v>
+        <v>92046</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -2873,7 +2873,7 @@
         <v>135593865</v>
       </c>
       <c r="B21" t="n">
-        <v>99191</v>
+        <v>99193</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2985,7 +2985,7 @@
         <v>135593892</v>
       </c>
       <c r="B22" t="n">
-        <v>99191</v>
+        <v>99193</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3097,7 +3097,7 @@
         <v>135593867</v>
       </c>
       <c r="B23" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3214,7 +3214,7 @@
         <v>135593868</v>
       </c>
       <c r="B24" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3331,7 +3331,7 @@
         <v>135593869</v>
       </c>
       <c r="B25" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3448,7 +3448,7 @@
         <v>135593872</v>
       </c>
       <c r="B26" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3565,7 +3565,7 @@
         <v>135593873</v>
       </c>
       <c r="B27" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3682,7 +3682,7 @@
         <v>135593874</v>
       </c>
       <c r="B28" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3799,7 +3799,7 @@
         <v>135593887</v>
       </c>
       <c r="B29" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3921,7 +3921,7 @@
         <v>135593891</v>
       </c>
       <c r="B30" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4038,7 +4038,7 @@
         <v>135593893</v>
       </c>
       <c r="B31" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4155,7 +4155,7 @@
         <v>135593894</v>
       </c>
       <c r="B32" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4272,7 +4272,7 @@
         <v>135593896</v>
       </c>
       <c r="B33" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 28104-2026 artfynd.xlsx
+++ b/artfynd/A 28104-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ37"/>
+  <dimension ref="A1:AZ34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2263,10 +2263,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>135593860</v>
+        <v>135593878</v>
       </c>
       <c r="B16" t="n">
-        <v>57980</v>
+        <v>58141</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2274,34 +2274,50 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>A 28104-2026, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>479454</v>
+        <v>479226</v>
       </c>
       <c r="R16" t="n">
-        <v>6991460</v>
+        <v>6991173</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2333,7 +2349,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2343,12 +2359,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:19</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre spår</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2374,16 +2385,16 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135593860</t>
+          <t>https://artportalen.se/Sighting/135593878</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>135593861</v>
+        <v>135593882</v>
       </c>
       <c r="B17" t="n">
-        <v>57980</v>
+        <v>58141</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2391,37 +2402,53 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>A 28104-2026, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>479449</v>
+        <v>479269</v>
       </c>
       <c r="R17" t="n">
-        <v>6991399</v>
+        <v>6991246</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2450,7 +2477,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2460,12 +2487,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:26</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2491,38 +2513,38 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135593861</t>
+          <t>https://artportalen.se/Sighting/135593882</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>135593877</v>
+        <v>135593865</v>
       </c>
       <c r="B18" t="n">
-        <v>57980</v>
+        <v>99193</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>219790</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2532,10 +2554,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>479282</v>
+        <v>479382</v>
       </c>
       <c r="R18" t="n">
-        <v>6991184</v>
+        <v>6991189</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2567,7 +2589,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2577,12 +2599,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16:09</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2608,67 +2625,51 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135593877</t>
+          <t>https://artportalen.se/Sighting/135593865</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>135593878</v>
+        <v>135593892</v>
       </c>
       <c r="B19" t="n">
-        <v>58141</v>
+        <v>99193</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103021</v>
+        <v>219790</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>A 28104-2026, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>479226</v>
+        <v>479323</v>
       </c>
       <c r="R19" t="n">
-        <v>6991173</v>
+        <v>6991354</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2700,7 +2701,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2710,7 +2711,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2736,70 +2737,54 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135593878</t>
+          <t>https://artportalen.se/Sighting/135593892</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>135593882</v>
+        <v>135593867</v>
       </c>
       <c r="B20" t="n">
-        <v>58141</v>
+        <v>99276</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>A 28104-2026, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>479269</v>
+        <v>479392</v>
       </c>
       <c r="R20" t="n">
-        <v>6991246</v>
+        <v>6991092</v>
       </c>
       <c r="S20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2828,7 +2813,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2838,7 +2823,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Räknat till 25 plantor utspritt</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2864,38 +2854,38 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135593882</t>
+          <t>https://artportalen.se/Sighting/135593867</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>135593865</v>
+        <v>135593868</v>
       </c>
       <c r="B21" t="n">
-        <v>99193</v>
+        <v>99276</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2905,10 +2895,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>479382</v>
+        <v>479398</v>
       </c>
       <c r="R21" t="n">
-        <v>6991189</v>
+        <v>6991100</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2940,7 +2930,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2950,7 +2940,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>15:29</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Räknat till 11 plantor utspridda</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2976,38 +2971,38 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135593865</t>
+          <t>https://artportalen.se/Sighting/135593868</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>135593892</v>
+        <v>135593869</v>
       </c>
       <c r="B22" t="n">
-        <v>99193</v>
+        <v>99276</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3017,10 +3012,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>479323</v>
+        <v>479399</v>
       </c>
       <c r="R22" t="n">
-        <v>6991354</v>
+        <v>6991106</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3052,7 +3047,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3062,7 +3057,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>15:34</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>5 plantor</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3088,13 +3088,13 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135593892</t>
+          <t>https://artportalen.se/Sighting/135593869</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>135593867</v>
+        <v>135593872</v>
       </c>
       <c r="B23" t="n">
         <v>99276</v>
@@ -3129,10 +3129,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>479392</v>
+        <v>479402</v>
       </c>
       <c r="R23" t="n">
-        <v>6991092</v>
+        <v>6991103</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3164,7 +3164,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3174,12 +3174,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Räknat till 25 plantor utspritt</t>
+          <t>Över 20 plantor samlat. En blomstjälk.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3205,13 +3205,13 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135593867</t>
+          <t>https://artportalen.se/Sighting/135593872</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>135593868</v>
+        <v>135593873</v>
       </c>
       <c r="B24" t="n">
         <v>99276</v>
@@ -3246,10 +3246,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>479398</v>
+        <v>479406</v>
       </c>
       <c r="R24" t="n">
-        <v>6991100</v>
+        <v>6991091</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3281,7 +3281,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3291,12 +3291,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Räknat till 11 plantor utspridda</t>
+          <t>Räknat till 5 utspridda plantor</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3322,13 +3322,13 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135593868</t>
+          <t>https://artportalen.se/Sighting/135593873</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>135593869</v>
+        <v>135593874</v>
       </c>
       <c r="B25" t="n">
         <v>99276</v>
@@ -3363,13 +3363,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>479399</v>
+        <v>479382</v>
       </c>
       <c r="R25" t="n">
-        <v>6991106</v>
+        <v>6991087</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3398,7 +3398,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3408,12 +3408,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>5 plantor</t>
+          <t>3 plantor</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3439,13 +3439,13 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135593869</t>
+          <t>https://artportalen.se/Sighting/135593874</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>135593872</v>
+        <v>135593887</v>
       </c>
       <c r="B26" t="n">
         <v>99276</v>
@@ -3474,16 +3474,21 @@
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>A 28104-2026, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>479402</v>
+        <v>479354</v>
       </c>
       <c r="R26" t="n">
-        <v>6991103</v>
+        <v>6991311</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3515,7 +3520,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3525,12 +3530,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Över 20 plantor samlat. En blomstjälk.</t>
+          <t>Ca 15 funna plantor</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3556,13 +3561,13 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135593872</t>
+          <t>https://artportalen.se/Sighting/135593887</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>135593873</v>
+        <v>135593891</v>
       </c>
       <c r="B27" t="n">
         <v>99276</v>
@@ -3597,10 +3602,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>479406</v>
+        <v>479329</v>
       </c>
       <c r="R27" t="n">
-        <v>6991091</v>
+        <v>6991351</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3632,7 +3637,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3642,12 +3647,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Räknat till 5 utspridda plantor</t>
+          <t>Över 30 funna plantor, ganska samlat</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3673,13 +3678,13 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135593873</t>
+          <t>https://artportalen.se/Sighting/135593891</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>135593874</v>
+        <v>135593893</v>
       </c>
       <c r="B28" t="n">
         <v>99276</v>
@@ -3714,13 +3719,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>479382</v>
+        <v>479325</v>
       </c>
       <c r="R28" t="n">
-        <v>6991087</v>
+        <v>6991383</v>
       </c>
       <c r="S28" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3749,7 +3754,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3759,12 +3764,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>3 plantor</t>
+          <t>Småplantor, över 30 st samlat</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3790,13 +3795,13 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135593874</t>
+          <t>https://artportalen.se/Sighting/135593893</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>135593887</v>
+        <v>135593894</v>
       </c>
       <c r="B29" t="n">
         <v>99276</v>
@@ -3825,21 +3830,16 @@
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>A 28104-2026, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>479354</v>
+        <v>479281</v>
       </c>
       <c r="R29" t="n">
-        <v>6991311</v>
+        <v>6991365</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3861,7 +3861,7 @@
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>Näs</t>
+          <t>Sunne</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
@@ -3871,7 +3871,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3881,12 +3881,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ca 15 funna plantor</t>
+          <t>Ca 10 plantor utspridda</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3912,13 +3912,13 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135593887</t>
+          <t>https://artportalen.se/Sighting/135593894</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>135593891</v>
+        <v>135593896</v>
       </c>
       <c r="B30" t="n">
         <v>99276</v>
@@ -3953,10 +3953,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>479329</v>
+        <v>479220</v>
       </c>
       <c r="R30" t="n">
-        <v>6991351</v>
+        <v>6991333</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>Näs</t>
+          <t>Sunne</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
@@ -3988,7 +3988,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3998,12 +3998,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Över 30 funna plantor, ganska samlat</t>
+          <t>3 st plantor</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4029,38 +4029,38 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135593891</t>
+          <t>https://artportalen.se/Sighting/135593896</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>135593893</v>
+        <v>135593859</v>
       </c>
       <c r="B31" t="n">
-        <v>99276</v>
+        <v>78450</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>228579</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4070,10 +4070,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>479325</v>
+        <v>479428</v>
       </c>
       <c r="R31" t="n">
-        <v>6991383</v>
+        <v>6991450</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4105,7 +4105,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4115,12 +4115,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>17:16</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Småplantor, över 30 st samlat</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4146,38 +4141,38 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135593893</t>
+          <t>https://artportalen.se/Sighting/135593859</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>135593894</v>
+        <v>135593862</v>
       </c>
       <c r="B32" t="n">
-        <v>99276</v>
+        <v>78450</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>228579</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4187,10 +4182,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>479281</v>
+        <v>479453</v>
       </c>
       <c r="R32" t="n">
-        <v>6991365</v>
+        <v>6991398</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4212,7 +4207,7 @@
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>Sunne</t>
+          <t>Näs</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
@@ -4222,7 +4217,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4232,12 +4227,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>17:23</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Ca 10 plantor utspridda</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4263,38 +4253,38 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135593894</t>
+          <t>https://artportalen.se/Sighting/135593862</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>135593896</v>
+        <v>135593870</v>
       </c>
       <c r="B33" t="n">
-        <v>99276</v>
+        <v>78450</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>228579</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4304,10 +4294,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>479220</v>
+        <v>479402</v>
       </c>
       <c r="R33" t="n">
-        <v>6991333</v>
+        <v>6991104</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4329,7 +4319,7 @@
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>Sunne</t>
+          <t>Näs</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr">
@@ -4339,7 +4329,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4349,12 +4339,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>17:32</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>3 st plantor</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4380,13 +4365,13 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135593896</t>
+          <t>https://artportalen.se/Sighting/135593870</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>135593859</v>
+        <v>135593880</v>
       </c>
       <c r="B34" t="n">
         <v>78450</v>
@@ -4421,10 +4406,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>479428</v>
+        <v>479188</v>
       </c>
       <c r="R34" t="n">
-        <v>6991450</v>
+        <v>6991204</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4456,7 +4441,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4466,7 +4451,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4491,342 +4476,6 @@
       </c>
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135593859</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="n">
-        <v>135593862</v>
-      </c>
-      <c r="B35" t="n">
-        <v>78450</v>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E35" t="n">
-        <v>228579</v>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>Liten svartspik</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>Chaenothecopsis nana</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>A 28104-2026, Jmt</t>
-        </is>
-      </c>
-      <c r="Q35" t="n">
-        <v>479453</v>
-      </c>
-      <c r="R35" t="n">
-        <v>6991398</v>
-      </c>
-      <c r="S35" t="n">
-        <v>5</v>
-      </c>
-      <c r="T35" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U35" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V35" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W35" t="inlineStr">
-        <is>
-          <t>Näs</t>
-        </is>
-      </c>
-      <c r="Y35" t="inlineStr">
-        <is>
-          <t>2026-07-26</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>14:32</t>
-        </is>
-      </c>
-      <c r="AA35" t="inlineStr">
-        <is>
-          <t>2026-07-26</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>14:32</t>
-        </is>
-      </c>
-      <c r="AD35" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE35" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG35" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT35" t="inlineStr"/>
-      <c r="AW35" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX35" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY35" t="inlineStr"/>
-      <c r="AZ35" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135593862</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="n">
-        <v>135593870</v>
-      </c>
-      <c r="B36" t="n">
-        <v>78450</v>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E36" t="n">
-        <v>228579</v>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>Liten svartspik</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>Chaenothecopsis nana</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>A 28104-2026, Jmt</t>
-        </is>
-      </c>
-      <c r="Q36" t="n">
-        <v>479402</v>
-      </c>
-      <c r="R36" t="n">
-        <v>6991104</v>
-      </c>
-      <c r="S36" t="n">
-        <v>5</v>
-      </c>
-      <c r="T36" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U36" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V36" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W36" t="inlineStr">
-        <is>
-          <t>Näs</t>
-        </is>
-      </c>
-      <c r="Y36" t="inlineStr">
-        <is>
-          <t>2026-07-26</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>15:38</t>
-        </is>
-      </c>
-      <c r="AA36" t="inlineStr">
-        <is>
-          <t>2026-07-26</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>15:38</t>
-        </is>
-      </c>
-      <c r="AD36" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE36" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG36" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT36" t="inlineStr"/>
-      <c r="AW36" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX36" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY36" t="inlineStr"/>
-      <c r="AZ36" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135593870</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="n">
-        <v>135593880</v>
-      </c>
-      <c r="B37" t="n">
-        <v>78450</v>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E37" t="n">
-        <v>228579</v>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>Liten svartspik</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>Chaenothecopsis nana</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>A 28104-2026, Jmt</t>
-        </is>
-      </c>
-      <c r="Q37" t="n">
-        <v>479188</v>
-      </c>
-      <c r="R37" t="n">
-        <v>6991204</v>
-      </c>
-      <c r="S37" t="n">
-        <v>5</v>
-      </c>
-      <c r="T37" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U37" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V37" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W37" t="inlineStr">
-        <is>
-          <t>Näs</t>
-        </is>
-      </c>
-      <c r="Y37" t="inlineStr">
-        <is>
-          <t>2026-07-26</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>16:26</t>
-        </is>
-      </c>
-      <c r="AA37" t="inlineStr">
-        <is>
-          <t>2026-07-26</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>16:26</t>
-        </is>
-      </c>
-      <c r="AD37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT37" t="inlineStr"/>
-      <c r="AW37" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX37" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY37" t="inlineStr"/>
-      <c r="AZ37" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135593880</t>
         </is>
@@ -4867,9 +4516,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 28104-2026 artfynd.xlsx
+++ b/artfynd/A 28104-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ34"/>
+  <dimension ref="A1:AZ37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2263,10 +2263,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>135593878</v>
+        <v>135593860</v>
       </c>
       <c r="B16" t="n">
-        <v>58141</v>
+        <v>57980</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2274,50 +2274,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>A 28104-2026, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>479226</v>
+        <v>479454</v>
       </c>
       <c r="R16" t="n">
-        <v>6991173</v>
+        <v>6991460</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2349,7 +2333,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2359,7 +2343,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>14:19</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre spår</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2385,16 +2374,16 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135593878</t>
+          <t>https://artportalen.se/Sighting/135593860</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>135593882</v>
+        <v>135593861</v>
       </c>
       <c r="B17" t="n">
-        <v>58141</v>
+        <v>57980</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2402,53 +2391,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>A 28104-2026, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>479269</v>
+        <v>479449</v>
       </c>
       <c r="R17" t="n">
-        <v>6991246</v>
+        <v>6991399</v>
       </c>
       <c r="S17" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2477,7 +2450,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2487,7 +2460,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>14:26</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2513,38 +2491,38 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135593882</t>
+          <t>https://artportalen.se/Sighting/135593861</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>135593865</v>
+        <v>135593877</v>
       </c>
       <c r="B18" t="n">
-        <v>99193</v>
+        <v>57980</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2554,10 +2532,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>479382</v>
+        <v>479282</v>
       </c>
       <c r="R18" t="n">
-        <v>6991189</v>
+        <v>6991184</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2589,7 +2567,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2599,7 +2577,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>16:09</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2625,51 +2608,67 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135593865</t>
+          <t>https://artportalen.se/Sighting/135593877</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>135593892</v>
+        <v>135593878</v>
       </c>
       <c r="B19" t="n">
-        <v>99193</v>
+        <v>58141</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>219790</v>
+        <v>103021</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>A 28104-2026, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>479323</v>
+        <v>479226</v>
       </c>
       <c r="R19" t="n">
-        <v>6991354</v>
+        <v>6991173</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2701,7 +2700,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2711,7 +2710,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2737,54 +2736,70 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135593892</t>
+          <t>https://artportalen.se/Sighting/135593878</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>135593867</v>
+        <v>135593882</v>
       </c>
       <c r="B20" t="n">
-        <v>99276</v>
+        <v>58141</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>A 28104-2026, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>479392</v>
+        <v>479269</v>
       </c>
       <c r="R20" t="n">
-        <v>6991092</v>
+        <v>6991246</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2813,7 +2828,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2823,12 +2838,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:25</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Räknat till 25 plantor utspritt</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2854,38 +2864,38 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135593867</t>
+          <t>https://artportalen.se/Sighting/135593882</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>135593868</v>
+        <v>135593865</v>
       </c>
       <c r="B21" t="n">
-        <v>99276</v>
+        <v>99193</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2895,10 +2905,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>479398</v>
+        <v>479382</v>
       </c>
       <c r="R21" t="n">
-        <v>6991100</v>
+        <v>6991189</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2930,7 +2940,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2940,12 +2950,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:29</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Räknat till 11 plantor utspridda</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2971,38 +2976,38 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135593868</t>
+          <t>https://artportalen.se/Sighting/135593865</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>135593869</v>
+        <v>135593892</v>
       </c>
       <c r="B22" t="n">
-        <v>99276</v>
+        <v>99193</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3012,10 +3017,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>479399</v>
+        <v>479323</v>
       </c>
       <c r="R22" t="n">
-        <v>6991106</v>
+        <v>6991354</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3047,7 +3052,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3057,12 +3062,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:34</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>5 plantor</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3088,13 +3088,13 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135593869</t>
+          <t>https://artportalen.se/Sighting/135593892</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>135593872</v>
+        <v>135593867</v>
       </c>
       <c r="B23" t="n">
         <v>99276</v>
@@ -3129,10 +3129,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>479402</v>
+        <v>479392</v>
       </c>
       <c r="R23" t="n">
-        <v>6991103</v>
+        <v>6991092</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3164,7 +3164,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3174,12 +3174,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Över 20 plantor samlat. En blomstjälk.</t>
+          <t>Räknat till 25 plantor utspritt</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3205,13 +3205,13 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135593872</t>
+          <t>https://artportalen.se/Sighting/135593867</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>135593873</v>
+        <v>135593868</v>
       </c>
       <c r="B24" t="n">
         <v>99276</v>
@@ -3246,10 +3246,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>479406</v>
+        <v>479398</v>
       </c>
       <c r="R24" t="n">
-        <v>6991091</v>
+        <v>6991100</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3281,7 +3281,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3291,12 +3291,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Räknat till 5 utspridda plantor</t>
+          <t>Räknat till 11 plantor utspridda</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3322,13 +3322,13 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135593873</t>
+          <t>https://artportalen.se/Sighting/135593868</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>135593874</v>
+        <v>135593869</v>
       </c>
       <c r="B25" t="n">
         <v>99276</v>
@@ -3363,13 +3363,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>479382</v>
+        <v>479399</v>
       </c>
       <c r="R25" t="n">
-        <v>6991087</v>
+        <v>6991106</v>
       </c>
       <c r="S25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3398,7 +3398,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3408,12 +3408,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>3 plantor</t>
+          <t>5 plantor</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3439,13 +3439,13 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135593874</t>
+          <t>https://artportalen.se/Sighting/135593869</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>135593887</v>
+        <v>135593872</v>
       </c>
       <c r="B26" t="n">
         <v>99276</v>
@@ -3474,21 +3474,16 @@
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>A 28104-2026, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>479354</v>
+        <v>479402</v>
       </c>
       <c r="R26" t="n">
-        <v>6991311</v>
+        <v>6991103</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3520,7 +3515,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3530,12 +3525,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ca 15 funna plantor</t>
+          <t>Över 20 plantor samlat. En blomstjälk.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3561,13 +3556,13 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135593887</t>
+          <t>https://artportalen.se/Sighting/135593872</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>135593891</v>
+        <v>135593873</v>
       </c>
       <c r="B27" t="n">
         <v>99276</v>
@@ -3602,10 +3597,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>479329</v>
+        <v>479406</v>
       </c>
       <c r="R27" t="n">
-        <v>6991351</v>
+        <v>6991091</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3637,7 +3632,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3647,12 +3642,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Över 30 funna plantor, ganska samlat</t>
+          <t>Räknat till 5 utspridda plantor</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3678,13 +3673,13 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135593891</t>
+          <t>https://artportalen.se/Sighting/135593873</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>135593893</v>
+        <v>135593874</v>
       </c>
       <c r="B28" t="n">
         <v>99276</v>
@@ -3719,13 +3714,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>479325</v>
+        <v>479382</v>
       </c>
       <c r="R28" t="n">
-        <v>6991383</v>
+        <v>6991087</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3754,7 +3749,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3764,12 +3759,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Småplantor, över 30 st samlat</t>
+          <t>3 plantor</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3795,13 +3790,13 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135593893</t>
+          <t>https://artportalen.se/Sighting/135593874</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>135593894</v>
+        <v>135593887</v>
       </c>
       <c r="B29" t="n">
         <v>99276</v>
@@ -3830,16 +3825,21 @@
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>A 28104-2026, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>479281</v>
+        <v>479354</v>
       </c>
       <c r="R29" t="n">
-        <v>6991365</v>
+        <v>6991311</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3861,7 +3861,7 @@
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>Sunne</t>
+          <t>Näs</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
@@ -3871,7 +3871,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3881,12 +3881,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ca 10 plantor utspridda</t>
+          <t>Ca 15 funna plantor</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3912,13 +3912,13 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135593894</t>
+          <t>https://artportalen.se/Sighting/135593887</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>135593896</v>
+        <v>135593891</v>
       </c>
       <c r="B30" t="n">
         <v>99276</v>
@@ -3953,10 +3953,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>479220</v>
+        <v>479329</v>
       </c>
       <c r="R30" t="n">
-        <v>6991333</v>
+        <v>6991351</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>Sunne</t>
+          <t>Näs</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
@@ -3988,7 +3988,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3998,12 +3998,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>3 st plantor</t>
+          <t>Över 30 funna plantor, ganska samlat</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4029,38 +4029,38 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135593896</t>
+          <t>https://artportalen.se/Sighting/135593891</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>135593859</v>
+        <v>135593893</v>
       </c>
       <c r="B31" t="n">
-        <v>78450</v>
+        <v>99276</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>228579</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4070,10 +4070,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>479428</v>
+        <v>479325</v>
       </c>
       <c r="R31" t="n">
-        <v>6991450</v>
+        <v>6991383</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4105,7 +4105,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4115,7 +4115,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>17:16</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Småplantor, över 30 st samlat</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4141,38 +4146,38 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135593859</t>
+          <t>https://artportalen.se/Sighting/135593893</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>135593862</v>
+        <v>135593894</v>
       </c>
       <c r="B32" t="n">
-        <v>78450</v>
+        <v>99276</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>228579</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4182,10 +4187,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>479453</v>
+        <v>479281</v>
       </c>
       <c r="R32" t="n">
-        <v>6991398</v>
+        <v>6991365</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4207,7 +4212,7 @@
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>Näs</t>
+          <t>Sunne</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
@@ -4217,7 +4222,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4227,7 +4232,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>17:23</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ca 10 plantor utspridda</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4253,38 +4263,38 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135593862</t>
+          <t>https://artportalen.se/Sighting/135593894</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>135593870</v>
+        <v>135593896</v>
       </c>
       <c r="B33" t="n">
-        <v>78450</v>
+        <v>99276</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>228579</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4294,10 +4304,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>479402</v>
+        <v>479220</v>
       </c>
       <c r="R33" t="n">
-        <v>6991104</v>
+        <v>6991333</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4319,7 +4329,7 @@
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>Näs</t>
+          <t>Sunne</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr">
@@ -4329,7 +4339,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4339,7 +4349,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>17:32</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>3 st plantor</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4365,13 +4380,13 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135593870</t>
+          <t>https://artportalen.se/Sighting/135593896</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>135593880</v>
+        <v>135593859</v>
       </c>
       <c r="B34" t="n">
         <v>78450</v>
@@ -4406,10 +4421,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>479188</v>
+        <v>479428</v>
       </c>
       <c r="R34" t="n">
-        <v>6991204</v>
+        <v>6991450</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4441,7 +4456,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4451,7 +4466,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4476,6 +4491,342 @@
       </c>
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135593859</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>135593862</v>
+      </c>
+      <c r="B35" t="n">
+        <v>78450</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>228579</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Liten svartspik</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis nana</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>A 28104-2026, Jmt</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>479453</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6991398</v>
+      </c>
+      <c r="S35" t="n">
+        <v>5</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Näs</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>14:32</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>14:32</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135593862</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>135593870</v>
+      </c>
+      <c r="B36" t="n">
+        <v>78450</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>228579</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Liten svartspik</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis nana</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>A 28104-2026, Jmt</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>479402</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6991104</v>
+      </c>
+      <c r="S36" t="n">
+        <v>5</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Näs</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>15:38</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>15:38</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135593870</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>135593880</v>
+      </c>
+      <c r="B37" t="n">
+        <v>78450</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>228579</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Liten svartspik</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis nana</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>A 28104-2026, Jmt</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>479188</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6991204</v>
+      </c>
+      <c r="S37" t="n">
+        <v>5</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Näs</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>16:26</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>16:26</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135593880</t>
         </is>
@@ -4516,6 +4867,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 28104-2026 artfynd.xlsx
+++ b/artfynd/A 28104-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135593890</v>
       </c>
       <c r="B2" t="n">
-        <v>92046</v>
+        <v>92060</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135593864</v>
       </c>
       <c r="B3" t="n">
-        <v>83292</v>
+        <v>83294</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135593858</v>
       </c>
       <c r="B4" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135593866</v>
       </c>
       <c r="B5" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135593883</v>
       </c>
       <c r="B6" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1248,7 +1248,7 @@
         <v>135593884</v>
       </c>
       <c r="B7" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         <v>135593885</v>
       </c>
       <c r="B8" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>135593886</v>
       </c>
       <c r="B9" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
         <v>135593895</v>
       </c>
       <c r="B10" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1701,7 +1701,7 @@
         <v>135593863</v>
       </c>
       <c r="B11" t="n">
-        <v>83428</v>
+        <v>83430</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1813,7 +1813,7 @@
         <v>135593871</v>
       </c>
       <c r="B12" t="n">
-        <v>83428</v>
+        <v>83430</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1925,7 +1925,7 @@
         <v>135593881</v>
       </c>
       <c r="B13" t="n">
-        <v>83428</v>
+        <v>83430</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2037,7 +2037,7 @@
         <v>135593889</v>
       </c>
       <c r="B14" t="n">
-        <v>83428</v>
+        <v>83430</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
         <v>135593875</v>
       </c>
       <c r="B15" t="n">
-        <v>57977</v>
+        <v>57979</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2266,7 +2266,7 @@
         <v>135593860</v>
       </c>
       <c r="B16" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2383,7 +2383,7 @@
         <v>135593861</v>
       </c>
       <c r="B17" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2500,7 +2500,7 @@
         <v>135593877</v>
       </c>
       <c r="B18" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2617,7 +2617,7 @@
         <v>135593878</v>
       </c>
       <c r="B19" t="n">
-        <v>58141</v>
+        <v>58143</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2745,7 +2745,7 @@
         <v>135593882</v>
       </c>
       <c r="B20" t="n">
-        <v>58141</v>
+        <v>58143</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2873,7 +2873,7 @@
         <v>135593865</v>
       </c>
       <c r="B21" t="n">
-        <v>99193</v>
+        <v>99210</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2985,7 +2985,7 @@
         <v>135593892</v>
       </c>
       <c r="B22" t="n">
-        <v>99193</v>
+        <v>99210</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3097,7 +3097,7 @@
         <v>135593867</v>
       </c>
       <c r="B23" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3214,7 +3214,7 @@
         <v>135593868</v>
       </c>
       <c r="B24" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3331,7 +3331,7 @@
         <v>135593869</v>
       </c>
       <c r="B25" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3448,7 +3448,7 @@
         <v>135593872</v>
       </c>
       <c r="B26" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3565,7 +3565,7 @@
         <v>135593873</v>
       </c>
       <c r="B27" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3682,7 +3682,7 @@
         <v>135593874</v>
       </c>
       <c r="B28" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3799,7 +3799,7 @@
         <v>135593887</v>
       </c>
       <c r="B29" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3921,7 +3921,7 @@
         <v>135593891</v>
       </c>
       <c r="B30" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4038,7 +4038,7 @@
         <v>135593893</v>
       </c>
       <c r="B31" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4155,7 +4155,7 @@
         <v>135593894</v>
       </c>
       <c r="B32" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4272,7 +4272,7 @@
         <v>135593896</v>
       </c>
       <c r="B33" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4389,7 +4389,7 @@
         <v>135593859</v>
       </c>
       <c r="B34" t="n">
-        <v>78450</v>
+        <v>78452</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4501,7 +4501,7 @@
         <v>135593862</v>
       </c>
       <c r="B35" t="n">
-        <v>78450</v>
+        <v>78452</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4613,7 +4613,7 @@
         <v>135593870</v>
       </c>
       <c r="B36" t="n">
-        <v>78450</v>
+        <v>78452</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4725,7 +4725,7 @@
         <v>135593880</v>
       </c>
       <c r="B37" t="n">
-        <v>78450</v>
+        <v>78452</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 28104-2026 artfynd.xlsx
+++ b/artfynd/A 28104-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ37"/>
+  <dimension ref="A1:AZ34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2263,10 +2263,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>135593860</v>
+        <v>135593878</v>
       </c>
       <c r="B16" t="n">
-        <v>57982</v>
+        <v>58143</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2274,34 +2274,50 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>A 28104-2026, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>479454</v>
+        <v>479226</v>
       </c>
       <c r="R16" t="n">
-        <v>6991460</v>
+        <v>6991173</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2333,7 +2349,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2343,12 +2359,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:19</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre spår</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2374,16 +2385,16 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135593860</t>
+          <t>https://artportalen.se/Sighting/135593878</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>135593861</v>
+        <v>135593882</v>
       </c>
       <c r="B17" t="n">
-        <v>57982</v>
+        <v>58143</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2391,37 +2402,53 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>A 28104-2026, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>479449</v>
+        <v>479269</v>
       </c>
       <c r="R17" t="n">
-        <v>6991399</v>
+        <v>6991246</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2450,7 +2477,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2460,12 +2487,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:26</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2491,38 +2513,38 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135593861</t>
+          <t>https://artportalen.se/Sighting/135593882</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>135593877</v>
+        <v>135593865</v>
       </c>
       <c r="B18" t="n">
-        <v>57982</v>
+        <v>99210</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>219790</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2532,10 +2554,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>479282</v>
+        <v>479382</v>
       </c>
       <c r="R18" t="n">
-        <v>6991184</v>
+        <v>6991189</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2567,7 +2589,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2577,12 +2599,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16:09</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2608,67 +2625,51 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135593877</t>
+          <t>https://artportalen.se/Sighting/135593865</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>135593878</v>
+        <v>135593892</v>
       </c>
       <c r="B19" t="n">
-        <v>58143</v>
+        <v>99210</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103021</v>
+        <v>219790</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>A 28104-2026, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>479226</v>
+        <v>479323</v>
       </c>
       <c r="R19" t="n">
-        <v>6991173</v>
+        <v>6991354</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2700,7 +2701,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2710,7 +2711,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2736,70 +2737,54 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135593878</t>
+          <t>https://artportalen.se/Sighting/135593892</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>135593882</v>
+        <v>135593867</v>
       </c>
       <c r="B20" t="n">
-        <v>58143</v>
+        <v>99293</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>A 28104-2026, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>479269</v>
+        <v>479392</v>
       </c>
       <c r="R20" t="n">
-        <v>6991246</v>
+        <v>6991092</v>
       </c>
       <c r="S20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2828,7 +2813,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2838,7 +2823,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Räknat till 25 plantor utspritt</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2864,38 +2854,38 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135593882</t>
+          <t>https://artportalen.se/Sighting/135593867</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>135593865</v>
+        <v>135593868</v>
       </c>
       <c r="B21" t="n">
-        <v>99210</v>
+        <v>99293</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2905,10 +2895,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>479382</v>
+        <v>479398</v>
       </c>
       <c r="R21" t="n">
-        <v>6991189</v>
+        <v>6991100</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2940,7 +2930,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2950,7 +2940,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>15:29</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Räknat till 11 plantor utspridda</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2976,38 +2971,38 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135593865</t>
+          <t>https://artportalen.se/Sighting/135593868</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>135593892</v>
+        <v>135593869</v>
       </c>
       <c r="B22" t="n">
-        <v>99210</v>
+        <v>99293</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3017,10 +3012,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>479323</v>
+        <v>479399</v>
       </c>
       <c r="R22" t="n">
-        <v>6991354</v>
+        <v>6991106</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3052,7 +3047,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3062,7 +3057,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>15:34</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>5 plantor</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3088,13 +3088,13 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135593892</t>
+          <t>https://artportalen.se/Sighting/135593869</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>135593867</v>
+        <v>135593872</v>
       </c>
       <c r="B23" t="n">
         <v>99293</v>
@@ -3129,10 +3129,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>479392</v>
+        <v>479402</v>
       </c>
       <c r="R23" t="n">
-        <v>6991092</v>
+        <v>6991103</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3164,7 +3164,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3174,12 +3174,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Räknat till 25 plantor utspritt</t>
+          <t>Över 20 plantor samlat. En blomstjälk.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3205,13 +3205,13 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135593867</t>
+          <t>https://artportalen.se/Sighting/135593872</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>135593868</v>
+        <v>135593873</v>
       </c>
       <c r="B24" t="n">
         <v>99293</v>
@@ -3246,10 +3246,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>479398</v>
+        <v>479406</v>
       </c>
       <c r="R24" t="n">
-        <v>6991100</v>
+        <v>6991091</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3281,7 +3281,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3291,12 +3291,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Räknat till 11 plantor utspridda</t>
+          <t>Räknat till 5 utspridda plantor</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3322,13 +3322,13 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135593868</t>
+          <t>https://artportalen.se/Sighting/135593873</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>135593869</v>
+        <v>135593874</v>
       </c>
       <c r="B25" t="n">
         <v>99293</v>
@@ -3363,13 +3363,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>479399</v>
+        <v>479382</v>
       </c>
       <c r="R25" t="n">
-        <v>6991106</v>
+        <v>6991087</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3398,7 +3398,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3408,12 +3408,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>5 plantor</t>
+          <t>3 plantor</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3439,13 +3439,13 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135593869</t>
+          <t>https://artportalen.se/Sighting/135593874</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>135593872</v>
+        <v>135593887</v>
       </c>
       <c r="B26" t="n">
         <v>99293</v>
@@ -3474,16 +3474,21 @@
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>A 28104-2026, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>479402</v>
+        <v>479354</v>
       </c>
       <c r="R26" t="n">
-        <v>6991103</v>
+        <v>6991311</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3515,7 +3520,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3525,12 +3530,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Över 20 plantor samlat. En blomstjälk.</t>
+          <t>Ca 15 funna plantor</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3556,13 +3561,13 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135593872</t>
+          <t>https://artportalen.se/Sighting/135593887</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>135593873</v>
+        <v>135593891</v>
       </c>
       <c r="B27" t="n">
         <v>99293</v>
@@ -3597,10 +3602,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>479406</v>
+        <v>479329</v>
       </c>
       <c r="R27" t="n">
-        <v>6991091</v>
+        <v>6991351</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3632,7 +3637,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3642,12 +3647,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Räknat till 5 utspridda plantor</t>
+          <t>Över 30 funna plantor, ganska samlat</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3673,13 +3678,13 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135593873</t>
+          <t>https://artportalen.se/Sighting/135593891</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>135593874</v>
+        <v>135593893</v>
       </c>
       <c r="B28" t="n">
         <v>99293</v>
@@ -3714,13 +3719,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>479382</v>
+        <v>479325</v>
       </c>
       <c r="R28" t="n">
-        <v>6991087</v>
+        <v>6991383</v>
       </c>
       <c r="S28" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3749,7 +3754,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3759,12 +3764,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>3 plantor</t>
+          <t>Småplantor, över 30 st samlat</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3790,13 +3795,13 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135593874</t>
+          <t>https://artportalen.se/Sighting/135593893</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>135593887</v>
+        <v>135593894</v>
       </c>
       <c r="B29" t="n">
         <v>99293</v>
@@ -3825,21 +3830,16 @@
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>A 28104-2026, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>479354</v>
+        <v>479281</v>
       </c>
       <c r="R29" t="n">
-        <v>6991311</v>
+        <v>6991365</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3861,7 +3861,7 @@
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>Näs</t>
+          <t>Sunne</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
@@ -3871,7 +3871,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3881,12 +3881,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ca 15 funna plantor</t>
+          <t>Ca 10 plantor utspridda</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3912,13 +3912,13 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135593887</t>
+          <t>https://artportalen.se/Sighting/135593894</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>135593891</v>
+        <v>135593896</v>
       </c>
       <c r="B30" t="n">
         <v>99293</v>
@@ -3953,10 +3953,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>479329</v>
+        <v>479220</v>
       </c>
       <c r="R30" t="n">
-        <v>6991351</v>
+        <v>6991333</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>Näs</t>
+          <t>Sunne</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
@@ -3988,7 +3988,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3998,12 +3998,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Över 30 funna plantor, ganska samlat</t>
+          <t>3 st plantor</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4029,38 +4029,38 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135593891</t>
+          <t>https://artportalen.se/Sighting/135593896</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>135593893</v>
+        <v>135593859</v>
       </c>
       <c r="B31" t="n">
-        <v>99293</v>
+        <v>78452</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>228579</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4070,10 +4070,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>479325</v>
+        <v>479428</v>
       </c>
       <c r="R31" t="n">
-        <v>6991383</v>
+        <v>6991450</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4105,7 +4105,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4115,12 +4115,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>17:16</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Småplantor, över 30 st samlat</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4146,38 +4141,38 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135593893</t>
+          <t>https://artportalen.se/Sighting/135593859</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>135593894</v>
+        <v>135593862</v>
       </c>
       <c r="B32" t="n">
-        <v>99293</v>
+        <v>78452</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>228579</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4187,10 +4182,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>479281</v>
+        <v>479453</v>
       </c>
       <c r="R32" t="n">
-        <v>6991365</v>
+        <v>6991398</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4212,7 +4207,7 @@
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>Sunne</t>
+          <t>Näs</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
@@ -4222,7 +4217,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4232,12 +4227,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>17:23</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Ca 10 plantor utspridda</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4263,38 +4253,38 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135593894</t>
+          <t>https://artportalen.se/Sighting/135593862</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>135593896</v>
+        <v>135593870</v>
       </c>
       <c r="B33" t="n">
-        <v>99293</v>
+        <v>78452</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>228579</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4304,10 +4294,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>479220</v>
+        <v>479402</v>
       </c>
       <c r="R33" t="n">
-        <v>6991333</v>
+        <v>6991104</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4329,7 +4319,7 @@
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>Sunne</t>
+          <t>Näs</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr">
@@ -4339,7 +4329,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4349,12 +4339,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>17:32</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>3 st plantor</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4380,13 +4365,13 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135593896</t>
+          <t>https://artportalen.se/Sighting/135593870</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>135593859</v>
+        <v>135593880</v>
       </c>
       <c r="B34" t="n">
         <v>78452</v>
@@ -4421,10 +4406,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>479428</v>
+        <v>479188</v>
       </c>
       <c r="R34" t="n">
-        <v>6991450</v>
+        <v>6991204</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4456,7 +4441,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4466,7 +4451,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4491,342 +4476,6 @@
       </c>
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135593859</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="n">
-        <v>135593862</v>
-      </c>
-      <c r="B35" t="n">
-        <v>78452</v>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E35" t="n">
-        <v>228579</v>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>Liten svartspik</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>Chaenothecopsis nana</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>A 28104-2026, Jmt</t>
-        </is>
-      </c>
-      <c r="Q35" t="n">
-        <v>479453</v>
-      </c>
-      <c r="R35" t="n">
-        <v>6991398</v>
-      </c>
-      <c r="S35" t="n">
-        <v>5</v>
-      </c>
-      <c r="T35" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U35" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V35" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W35" t="inlineStr">
-        <is>
-          <t>Näs</t>
-        </is>
-      </c>
-      <c r="Y35" t="inlineStr">
-        <is>
-          <t>2026-07-26</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>14:32</t>
-        </is>
-      </c>
-      <c r="AA35" t="inlineStr">
-        <is>
-          <t>2026-07-26</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>14:32</t>
-        </is>
-      </c>
-      <c r="AD35" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE35" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG35" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT35" t="inlineStr"/>
-      <c r="AW35" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX35" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY35" t="inlineStr"/>
-      <c r="AZ35" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135593862</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="n">
-        <v>135593870</v>
-      </c>
-      <c r="B36" t="n">
-        <v>78452</v>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E36" t="n">
-        <v>228579</v>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>Liten svartspik</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>Chaenothecopsis nana</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>A 28104-2026, Jmt</t>
-        </is>
-      </c>
-      <c r="Q36" t="n">
-        <v>479402</v>
-      </c>
-      <c r="R36" t="n">
-        <v>6991104</v>
-      </c>
-      <c r="S36" t="n">
-        <v>5</v>
-      </c>
-      <c r="T36" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U36" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V36" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W36" t="inlineStr">
-        <is>
-          <t>Näs</t>
-        </is>
-      </c>
-      <c r="Y36" t="inlineStr">
-        <is>
-          <t>2026-07-26</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>15:38</t>
-        </is>
-      </c>
-      <c r="AA36" t="inlineStr">
-        <is>
-          <t>2026-07-26</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>15:38</t>
-        </is>
-      </c>
-      <c r="AD36" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE36" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG36" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT36" t="inlineStr"/>
-      <c r="AW36" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX36" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY36" t="inlineStr"/>
-      <c r="AZ36" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135593870</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="n">
-        <v>135593880</v>
-      </c>
-      <c r="B37" t="n">
-        <v>78452</v>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E37" t="n">
-        <v>228579</v>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>Liten svartspik</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>Chaenothecopsis nana</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>A 28104-2026, Jmt</t>
-        </is>
-      </c>
-      <c r="Q37" t="n">
-        <v>479188</v>
-      </c>
-      <c r="R37" t="n">
-        <v>6991204</v>
-      </c>
-      <c r="S37" t="n">
-        <v>5</v>
-      </c>
-      <c r="T37" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U37" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V37" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W37" t="inlineStr">
-        <is>
-          <t>Näs</t>
-        </is>
-      </c>
-      <c r="Y37" t="inlineStr">
-        <is>
-          <t>2026-07-26</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>16:26</t>
-        </is>
-      </c>
-      <c r="AA37" t="inlineStr">
-        <is>
-          <t>2026-07-26</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>16:26</t>
-        </is>
-      </c>
-      <c r="AD37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT37" t="inlineStr"/>
-      <c r="AW37" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX37" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY37" t="inlineStr"/>
-      <c r="AZ37" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135593880</t>
         </is>
@@ -4867,9 +4516,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 28104-2026 artfynd.xlsx
+++ b/artfynd/A 28104-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ34"/>
+  <dimension ref="A1:AZ37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2263,10 +2263,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>135593878</v>
+        <v>135593860</v>
       </c>
       <c r="B16" t="n">
-        <v>58143</v>
+        <v>57982</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2274,50 +2274,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>A 28104-2026, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>479226</v>
+        <v>479454</v>
       </c>
       <c r="R16" t="n">
-        <v>6991173</v>
+        <v>6991460</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2349,7 +2333,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2359,7 +2343,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>14:19</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre spår</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2385,16 +2374,16 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135593878</t>
+          <t>https://artportalen.se/Sighting/135593860</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>135593882</v>
+        <v>135593861</v>
       </c>
       <c r="B17" t="n">
-        <v>58143</v>
+        <v>57982</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2402,53 +2391,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>A 28104-2026, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>479269</v>
+        <v>479449</v>
       </c>
       <c r="R17" t="n">
-        <v>6991246</v>
+        <v>6991399</v>
       </c>
       <c r="S17" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2477,7 +2450,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2487,7 +2460,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>14:26</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2513,38 +2491,38 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135593882</t>
+          <t>https://artportalen.se/Sighting/135593861</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>135593865</v>
+        <v>135593877</v>
       </c>
       <c r="B18" t="n">
-        <v>99210</v>
+        <v>57982</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2554,10 +2532,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>479382</v>
+        <v>479282</v>
       </c>
       <c r="R18" t="n">
-        <v>6991189</v>
+        <v>6991184</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2589,7 +2567,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2599,7 +2577,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>16:09</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2625,51 +2608,67 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135593865</t>
+          <t>https://artportalen.se/Sighting/135593877</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>135593892</v>
+        <v>135593878</v>
       </c>
       <c r="B19" t="n">
-        <v>99210</v>
+        <v>58143</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>219790</v>
+        <v>103021</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>A 28104-2026, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>479323</v>
+        <v>479226</v>
       </c>
       <c r="R19" t="n">
-        <v>6991354</v>
+        <v>6991173</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2701,7 +2700,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2711,7 +2710,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2737,54 +2736,70 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135593892</t>
+          <t>https://artportalen.se/Sighting/135593878</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>135593867</v>
+        <v>135593882</v>
       </c>
       <c r="B20" t="n">
-        <v>99293</v>
+        <v>58143</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>A 28104-2026, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>479392</v>
+        <v>479269</v>
       </c>
       <c r="R20" t="n">
-        <v>6991092</v>
+        <v>6991246</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2813,7 +2828,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2823,12 +2838,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:25</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Räknat till 25 plantor utspritt</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2854,38 +2864,38 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135593867</t>
+          <t>https://artportalen.se/Sighting/135593882</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>135593868</v>
+        <v>135593865</v>
       </c>
       <c r="B21" t="n">
-        <v>99293</v>
+        <v>99210</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2895,10 +2905,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>479398</v>
+        <v>479382</v>
       </c>
       <c r="R21" t="n">
-        <v>6991100</v>
+        <v>6991189</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2930,7 +2940,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2940,12 +2950,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:29</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Räknat till 11 plantor utspridda</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2971,38 +2976,38 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135593868</t>
+          <t>https://artportalen.se/Sighting/135593865</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>135593869</v>
+        <v>135593892</v>
       </c>
       <c r="B22" t="n">
-        <v>99293</v>
+        <v>99210</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3012,10 +3017,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>479399</v>
+        <v>479323</v>
       </c>
       <c r="R22" t="n">
-        <v>6991106</v>
+        <v>6991354</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3047,7 +3052,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3057,12 +3062,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:34</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>5 plantor</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3088,13 +3088,13 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135593869</t>
+          <t>https://artportalen.se/Sighting/135593892</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>135593872</v>
+        <v>135593867</v>
       </c>
       <c r="B23" t="n">
         <v>99293</v>
@@ -3129,10 +3129,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>479402</v>
+        <v>479392</v>
       </c>
       <c r="R23" t="n">
-        <v>6991103</v>
+        <v>6991092</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3164,7 +3164,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3174,12 +3174,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Över 20 plantor samlat. En blomstjälk.</t>
+          <t>Räknat till 25 plantor utspritt</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3205,13 +3205,13 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135593872</t>
+          <t>https://artportalen.se/Sighting/135593867</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>135593873</v>
+        <v>135593868</v>
       </c>
       <c r="B24" t="n">
         <v>99293</v>
@@ -3246,10 +3246,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>479406</v>
+        <v>479398</v>
       </c>
       <c r="R24" t="n">
-        <v>6991091</v>
+        <v>6991100</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3281,7 +3281,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3291,12 +3291,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Räknat till 5 utspridda plantor</t>
+          <t>Räknat till 11 plantor utspridda</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3322,13 +3322,13 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135593873</t>
+          <t>https://artportalen.se/Sighting/135593868</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>135593874</v>
+        <v>135593869</v>
       </c>
       <c r="B25" t="n">
         <v>99293</v>
@@ -3363,13 +3363,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>479382</v>
+        <v>479399</v>
       </c>
       <c r="R25" t="n">
-        <v>6991087</v>
+        <v>6991106</v>
       </c>
       <c r="S25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3398,7 +3398,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3408,12 +3408,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>3 plantor</t>
+          <t>5 plantor</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3439,13 +3439,13 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135593874</t>
+          <t>https://artportalen.se/Sighting/135593869</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>135593887</v>
+        <v>135593872</v>
       </c>
       <c r="B26" t="n">
         <v>99293</v>
@@ -3474,21 +3474,16 @@
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>A 28104-2026, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>479354</v>
+        <v>479402</v>
       </c>
       <c r="R26" t="n">
-        <v>6991311</v>
+        <v>6991103</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3520,7 +3515,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3530,12 +3525,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ca 15 funna plantor</t>
+          <t>Över 20 plantor samlat. En blomstjälk.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3561,13 +3556,13 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135593887</t>
+          <t>https://artportalen.se/Sighting/135593872</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>135593891</v>
+        <v>135593873</v>
       </c>
       <c r="B27" t="n">
         <v>99293</v>
@@ -3602,10 +3597,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>479329</v>
+        <v>479406</v>
       </c>
       <c r="R27" t="n">
-        <v>6991351</v>
+        <v>6991091</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3637,7 +3632,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3647,12 +3642,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Över 30 funna plantor, ganska samlat</t>
+          <t>Räknat till 5 utspridda plantor</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3678,13 +3673,13 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135593891</t>
+          <t>https://artportalen.se/Sighting/135593873</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>135593893</v>
+        <v>135593874</v>
       </c>
       <c r="B28" t="n">
         <v>99293</v>
@@ -3719,13 +3714,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>479325</v>
+        <v>479382</v>
       </c>
       <c r="R28" t="n">
-        <v>6991383</v>
+        <v>6991087</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3754,7 +3749,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3764,12 +3759,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Småplantor, över 30 st samlat</t>
+          <t>3 plantor</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3795,13 +3790,13 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135593893</t>
+          <t>https://artportalen.se/Sighting/135593874</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>135593894</v>
+        <v>135593887</v>
       </c>
       <c r="B29" t="n">
         <v>99293</v>
@@ -3830,16 +3825,21 @@
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>A 28104-2026, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>479281</v>
+        <v>479354</v>
       </c>
       <c r="R29" t="n">
-        <v>6991365</v>
+        <v>6991311</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3861,7 +3861,7 @@
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>Sunne</t>
+          <t>Näs</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
@@ -3871,7 +3871,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3881,12 +3881,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ca 10 plantor utspridda</t>
+          <t>Ca 15 funna plantor</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3912,13 +3912,13 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135593894</t>
+          <t>https://artportalen.se/Sighting/135593887</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>135593896</v>
+        <v>135593891</v>
       </c>
       <c r="B30" t="n">
         <v>99293</v>
@@ -3953,10 +3953,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>479220</v>
+        <v>479329</v>
       </c>
       <c r="R30" t="n">
-        <v>6991333</v>
+        <v>6991351</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>Sunne</t>
+          <t>Näs</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
@@ -3988,7 +3988,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3998,12 +3998,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>3 st plantor</t>
+          <t>Över 30 funna plantor, ganska samlat</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4029,38 +4029,38 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135593896</t>
+          <t>https://artportalen.se/Sighting/135593891</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>135593859</v>
+        <v>135593893</v>
       </c>
       <c r="B31" t="n">
-        <v>78452</v>
+        <v>99293</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>228579</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4070,10 +4070,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>479428</v>
+        <v>479325</v>
       </c>
       <c r="R31" t="n">
-        <v>6991450</v>
+        <v>6991383</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4105,7 +4105,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4115,7 +4115,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>17:16</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Småplantor, över 30 st samlat</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4141,38 +4146,38 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135593859</t>
+          <t>https://artportalen.se/Sighting/135593893</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>135593862</v>
+        <v>135593894</v>
       </c>
       <c r="B32" t="n">
-        <v>78452</v>
+        <v>99293</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>228579</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4182,10 +4187,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>479453</v>
+        <v>479281</v>
       </c>
       <c r="R32" t="n">
-        <v>6991398</v>
+        <v>6991365</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4207,7 +4212,7 @@
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>Näs</t>
+          <t>Sunne</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
@@ -4217,7 +4222,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4227,7 +4232,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>17:23</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ca 10 plantor utspridda</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4253,38 +4263,38 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135593862</t>
+          <t>https://artportalen.se/Sighting/135593894</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>135593870</v>
+        <v>135593896</v>
       </c>
       <c r="B33" t="n">
-        <v>78452</v>
+        <v>99293</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>228579</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4294,10 +4304,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>479402</v>
+        <v>479220</v>
       </c>
       <c r="R33" t="n">
-        <v>6991104</v>
+        <v>6991333</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4319,7 +4329,7 @@
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>Näs</t>
+          <t>Sunne</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr">
@@ -4329,7 +4339,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4339,7 +4349,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>17:32</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>3 st plantor</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4365,13 +4380,13 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135593870</t>
+          <t>https://artportalen.se/Sighting/135593896</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>135593880</v>
+        <v>135593859</v>
       </c>
       <c r="B34" t="n">
         <v>78452</v>
@@ -4406,10 +4421,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>479188</v>
+        <v>479428</v>
       </c>
       <c r="R34" t="n">
-        <v>6991204</v>
+        <v>6991450</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4441,7 +4456,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4451,7 +4466,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4476,6 +4491,342 @@
       </c>
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135593859</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>135593862</v>
+      </c>
+      <c r="B35" t="n">
+        <v>78452</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>228579</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Liten svartspik</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis nana</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>A 28104-2026, Jmt</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>479453</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6991398</v>
+      </c>
+      <c r="S35" t="n">
+        <v>5</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Näs</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>14:32</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>14:32</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135593862</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>135593870</v>
+      </c>
+      <c r="B36" t="n">
+        <v>78452</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>228579</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Liten svartspik</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis nana</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>A 28104-2026, Jmt</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>479402</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6991104</v>
+      </c>
+      <c r="S36" t="n">
+        <v>5</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Näs</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>15:38</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>15:38</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135593870</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>135593880</v>
+      </c>
+      <c r="B37" t="n">
+        <v>78452</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>228579</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Liten svartspik</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis nana</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>A 28104-2026, Jmt</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>479188</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6991204</v>
+      </c>
+      <c r="S37" t="n">
+        <v>5</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Näs</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>16:26</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>16:26</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135593880</t>
         </is>
@@ -4516,6 +4867,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 28104-2026 artfynd.xlsx
+++ b/artfynd/A 28104-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135593890</v>
       </c>
       <c r="B2" t="n">
-        <v>92060</v>
+        <v>92061</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135593864</v>
       </c>
       <c r="B3" t="n">
-        <v>83294</v>
+        <v>83311</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135593858</v>
       </c>
       <c r="B4" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135593866</v>
       </c>
       <c r="B5" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135593883</v>
       </c>
       <c r="B6" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1248,7 +1248,7 @@
         <v>135593884</v>
       </c>
       <c r="B7" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         <v>135593885</v>
       </c>
       <c r="B8" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>135593886</v>
       </c>
       <c r="B9" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
         <v>135593895</v>
       </c>
       <c r="B10" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1701,7 +1701,7 @@
         <v>135593863</v>
       </c>
       <c r="B11" t="n">
-        <v>83430</v>
+        <v>83431</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1813,7 +1813,7 @@
         <v>135593871</v>
       </c>
       <c r="B12" t="n">
-        <v>83430</v>
+        <v>83431</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1925,7 +1925,7 @@
         <v>135593881</v>
       </c>
       <c r="B13" t="n">
-        <v>83430</v>
+        <v>83431</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2037,7 +2037,7 @@
         <v>135593889</v>
       </c>
       <c r="B14" t="n">
-        <v>83430</v>
+        <v>83431</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2873,7 +2873,7 @@
         <v>135593865</v>
       </c>
       <c r="B21" t="n">
-        <v>99210</v>
+        <v>99211</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2985,7 +2985,7 @@
         <v>135593892</v>
       </c>
       <c r="B22" t="n">
-        <v>99210</v>
+        <v>99211</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3097,7 +3097,7 @@
         <v>135593867</v>
       </c>
       <c r="B23" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3214,7 +3214,7 @@
         <v>135593868</v>
       </c>
       <c r="B24" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3331,7 +3331,7 @@
         <v>135593869</v>
       </c>
       <c r="B25" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3448,7 +3448,7 @@
         <v>135593872</v>
       </c>
       <c r="B26" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3565,7 +3565,7 @@
         <v>135593873</v>
       </c>
       <c r="B27" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3682,7 +3682,7 @@
         <v>135593874</v>
       </c>
       <c r="B28" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3799,7 +3799,7 @@
         <v>135593887</v>
       </c>
       <c r="B29" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3921,7 +3921,7 @@
         <v>135593891</v>
       </c>
       <c r="B30" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4038,7 +4038,7 @@
         <v>135593893</v>
       </c>
       <c r="B31" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4155,7 +4155,7 @@
         <v>135593894</v>
       </c>
       <c r="B32" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4272,7 +4272,7 @@
         <v>135593896</v>
       </c>
       <c r="B33" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4389,7 +4389,7 @@
         <v>135593859</v>
       </c>
       <c r="B34" t="n">
-        <v>78452</v>
+        <v>78453</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4501,7 +4501,7 @@
         <v>135593862</v>
       </c>
       <c r="B35" t="n">
-        <v>78452</v>
+        <v>78453</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4613,7 +4613,7 @@
         <v>135593870</v>
       </c>
       <c r="B36" t="n">
-        <v>78452</v>
+        <v>78453</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4725,7 +4725,7 @@
         <v>135593880</v>
       </c>
       <c r="B37" t="n">
-        <v>78452</v>
+        <v>78453</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 28104-2026 artfynd.xlsx
+++ b/artfynd/A 28104-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ37"/>
+  <dimension ref="A1:AZ34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -683,7 +683,7 @@
         <v>135593890</v>
       </c>
       <c r="B2" t="n">
-        <v>92061</v>
+        <v>92062</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -2263,10 +2263,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>135593860</v>
+        <v>135593878</v>
       </c>
       <c r="B16" t="n">
-        <v>57982</v>
+        <v>58143</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2274,34 +2274,50 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>A 28104-2026, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>479454</v>
+        <v>479226</v>
       </c>
       <c r="R16" t="n">
-        <v>6991460</v>
+        <v>6991173</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2333,7 +2349,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2343,12 +2359,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:19</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre spår</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2374,16 +2385,16 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135593860</t>
+          <t>https://artportalen.se/Sighting/135593878</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>135593861</v>
+        <v>135593882</v>
       </c>
       <c r="B17" t="n">
-        <v>57982</v>
+        <v>58143</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2391,37 +2402,53 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>A 28104-2026, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>479449</v>
+        <v>479269</v>
       </c>
       <c r="R17" t="n">
-        <v>6991399</v>
+        <v>6991246</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2450,7 +2477,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2460,12 +2487,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:26</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2491,38 +2513,38 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135593861</t>
+          <t>https://artportalen.se/Sighting/135593882</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>135593877</v>
+        <v>135593865</v>
       </c>
       <c r="B18" t="n">
-        <v>57982</v>
+        <v>99212</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>219790</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2532,10 +2554,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>479282</v>
+        <v>479382</v>
       </c>
       <c r="R18" t="n">
-        <v>6991184</v>
+        <v>6991189</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2567,7 +2589,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2577,12 +2599,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16:09</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2608,67 +2625,51 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135593877</t>
+          <t>https://artportalen.se/Sighting/135593865</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>135593878</v>
+        <v>135593892</v>
       </c>
       <c r="B19" t="n">
-        <v>58143</v>
+        <v>99212</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103021</v>
+        <v>219790</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>A 28104-2026, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>479226</v>
+        <v>479323</v>
       </c>
       <c r="R19" t="n">
-        <v>6991173</v>
+        <v>6991354</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2700,7 +2701,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2710,7 +2711,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2736,70 +2737,54 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135593878</t>
+          <t>https://artportalen.se/Sighting/135593892</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>135593882</v>
+        <v>135593867</v>
       </c>
       <c r="B20" t="n">
-        <v>58143</v>
+        <v>99295</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>A 28104-2026, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>479269</v>
+        <v>479392</v>
       </c>
       <c r="R20" t="n">
-        <v>6991246</v>
+        <v>6991092</v>
       </c>
       <c r="S20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2828,7 +2813,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2838,7 +2823,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Räknat till 25 plantor utspritt</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2864,38 +2854,38 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135593882</t>
+          <t>https://artportalen.se/Sighting/135593867</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>135593865</v>
+        <v>135593868</v>
       </c>
       <c r="B21" t="n">
-        <v>99211</v>
+        <v>99295</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2905,10 +2895,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>479382</v>
+        <v>479398</v>
       </c>
       <c r="R21" t="n">
-        <v>6991189</v>
+        <v>6991100</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2940,7 +2930,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2950,7 +2940,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>15:29</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Räknat till 11 plantor utspridda</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2976,38 +2971,38 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135593865</t>
+          <t>https://artportalen.se/Sighting/135593868</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>135593892</v>
+        <v>135593869</v>
       </c>
       <c r="B22" t="n">
-        <v>99211</v>
+        <v>99295</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3017,10 +3012,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>479323</v>
+        <v>479399</v>
       </c>
       <c r="R22" t="n">
-        <v>6991354</v>
+        <v>6991106</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3052,7 +3047,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3062,7 +3057,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>15:34</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>5 plantor</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3088,16 +3088,16 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135593892</t>
+          <t>https://artportalen.se/Sighting/135593869</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>135593867</v>
+        <v>135593872</v>
       </c>
       <c r="B23" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3129,10 +3129,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>479392</v>
+        <v>479402</v>
       </c>
       <c r="R23" t="n">
-        <v>6991092</v>
+        <v>6991103</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3164,7 +3164,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3174,12 +3174,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Räknat till 25 plantor utspritt</t>
+          <t>Över 20 plantor samlat. En blomstjälk.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3205,16 +3205,16 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135593867</t>
+          <t>https://artportalen.se/Sighting/135593872</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>135593868</v>
+        <v>135593873</v>
       </c>
       <c r="B24" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3246,10 +3246,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>479398</v>
+        <v>479406</v>
       </c>
       <c r="R24" t="n">
-        <v>6991100</v>
+        <v>6991091</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3281,7 +3281,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3291,12 +3291,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Räknat till 11 plantor utspridda</t>
+          <t>Räknat till 5 utspridda plantor</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3322,16 +3322,16 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135593868</t>
+          <t>https://artportalen.se/Sighting/135593873</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>135593869</v>
+        <v>135593874</v>
       </c>
       <c r="B25" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3363,13 +3363,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>479399</v>
+        <v>479382</v>
       </c>
       <c r="R25" t="n">
-        <v>6991106</v>
+        <v>6991087</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3398,7 +3398,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3408,12 +3408,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>5 plantor</t>
+          <t>3 plantor</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3439,16 +3439,16 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135593869</t>
+          <t>https://artportalen.se/Sighting/135593874</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>135593872</v>
+        <v>135593887</v>
       </c>
       <c r="B26" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3474,16 +3474,21 @@
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>A 28104-2026, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>479402</v>
+        <v>479354</v>
       </c>
       <c r="R26" t="n">
-        <v>6991103</v>
+        <v>6991311</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3515,7 +3520,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3525,12 +3530,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Över 20 plantor samlat. En blomstjälk.</t>
+          <t>Ca 15 funna plantor</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3556,16 +3561,16 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135593872</t>
+          <t>https://artportalen.se/Sighting/135593887</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>135593873</v>
+        <v>135593891</v>
       </c>
       <c r="B27" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3597,10 +3602,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>479406</v>
+        <v>479329</v>
       </c>
       <c r="R27" t="n">
-        <v>6991091</v>
+        <v>6991351</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3632,7 +3637,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3642,12 +3647,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Räknat till 5 utspridda plantor</t>
+          <t>Över 30 funna plantor, ganska samlat</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3673,16 +3678,16 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135593873</t>
+          <t>https://artportalen.se/Sighting/135593891</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>135593874</v>
+        <v>135593893</v>
       </c>
       <c r="B28" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3714,13 +3719,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>479382</v>
+        <v>479325</v>
       </c>
       <c r="R28" t="n">
-        <v>6991087</v>
+        <v>6991383</v>
       </c>
       <c r="S28" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3749,7 +3754,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3759,12 +3764,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>3 plantor</t>
+          <t>Småplantor, över 30 st samlat</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3790,16 +3795,16 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135593874</t>
+          <t>https://artportalen.se/Sighting/135593893</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>135593887</v>
+        <v>135593894</v>
       </c>
       <c r="B29" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3825,21 +3830,16 @@
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>A 28104-2026, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>479354</v>
+        <v>479281</v>
       </c>
       <c r="R29" t="n">
-        <v>6991311</v>
+        <v>6991365</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3861,7 +3861,7 @@
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>Näs</t>
+          <t>Sunne</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
@@ -3871,7 +3871,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3881,12 +3881,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ca 15 funna plantor</t>
+          <t>Ca 10 plantor utspridda</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3912,16 +3912,16 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135593887</t>
+          <t>https://artportalen.se/Sighting/135593894</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>135593891</v>
+        <v>135593896</v>
       </c>
       <c r="B30" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3953,10 +3953,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>479329</v>
+        <v>479220</v>
       </c>
       <c r="R30" t="n">
-        <v>6991351</v>
+        <v>6991333</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>Näs</t>
+          <t>Sunne</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
@@ -3988,7 +3988,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3998,12 +3998,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Över 30 funna plantor, ganska samlat</t>
+          <t>3 st plantor</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4029,38 +4029,38 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135593891</t>
+          <t>https://artportalen.se/Sighting/135593896</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>135593893</v>
+        <v>135593859</v>
       </c>
       <c r="B31" t="n">
-        <v>99294</v>
+        <v>78453</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>228579</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4070,10 +4070,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>479325</v>
+        <v>479428</v>
       </c>
       <c r="R31" t="n">
-        <v>6991383</v>
+        <v>6991450</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4105,7 +4105,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4115,12 +4115,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>17:16</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Småplantor, över 30 st samlat</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4146,38 +4141,38 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135593893</t>
+          <t>https://artportalen.se/Sighting/135593859</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>135593894</v>
+        <v>135593862</v>
       </c>
       <c r="B32" t="n">
-        <v>99294</v>
+        <v>78453</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>228579</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4187,10 +4182,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>479281</v>
+        <v>479453</v>
       </c>
       <c r="R32" t="n">
-        <v>6991365</v>
+        <v>6991398</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4212,7 +4207,7 @@
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>Sunne</t>
+          <t>Näs</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
@@ -4222,7 +4217,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4232,12 +4227,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>17:23</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Ca 10 plantor utspridda</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4263,38 +4253,38 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135593894</t>
+          <t>https://artportalen.se/Sighting/135593862</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>135593896</v>
+        <v>135593870</v>
       </c>
       <c r="B33" t="n">
-        <v>99294</v>
+        <v>78453</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>228579</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4304,10 +4294,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>479220</v>
+        <v>479402</v>
       </c>
       <c r="R33" t="n">
-        <v>6991333</v>
+        <v>6991104</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4329,7 +4319,7 @@
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>Sunne</t>
+          <t>Näs</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr">
@@ -4339,7 +4329,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4349,12 +4339,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>17:32</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>3 st plantor</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4380,13 +4365,13 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135593896</t>
+          <t>https://artportalen.se/Sighting/135593870</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>135593859</v>
+        <v>135593880</v>
       </c>
       <c r="B34" t="n">
         <v>78453</v>
@@ -4421,10 +4406,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>479428</v>
+        <v>479188</v>
       </c>
       <c r="R34" t="n">
-        <v>6991450</v>
+        <v>6991204</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4456,7 +4441,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4466,7 +4451,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4491,342 +4476,6 @@
       </c>
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135593859</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="n">
-        <v>135593862</v>
-      </c>
-      <c r="B35" t="n">
-        <v>78453</v>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E35" t="n">
-        <v>228579</v>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>Liten svartspik</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>Chaenothecopsis nana</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>A 28104-2026, Jmt</t>
-        </is>
-      </c>
-      <c r="Q35" t="n">
-        <v>479453</v>
-      </c>
-      <c r="R35" t="n">
-        <v>6991398</v>
-      </c>
-      <c r="S35" t="n">
-        <v>5</v>
-      </c>
-      <c r="T35" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U35" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V35" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W35" t="inlineStr">
-        <is>
-          <t>Näs</t>
-        </is>
-      </c>
-      <c r="Y35" t="inlineStr">
-        <is>
-          <t>2026-07-26</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>14:32</t>
-        </is>
-      </c>
-      <c r="AA35" t="inlineStr">
-        <is>
-          <t>2026-07-26</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>14:32</t>
-        </is>
-      </c>
-      <c r="AD35" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE35" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG35" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT35" t="inlineStr"/>
-      <c r="AW35" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX35" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY35" t="inlineStr"/>
-      <c r="AZ35" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135593862</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="n">
-        <v>135593870</v>
-      </c>
-      <c r="B36" t="n">
-        <v>78453</v>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E36" t="n">
-        <v>228579</v>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>Liten svartspik</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>Chaenothecopsis nana</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>A 28104-2026, Jmt</t>
-        </is>
-      </c>
-      <c r="Q36" t="n">
-        <v>479402</v>
-      </c>
-      <c r="R36" t="n">
-        <v>6991104</v>
-      </c>
-      <c r="S36" t="n">
-        <v>5</v>
-      </c>
-      <c r="T36" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U36" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V36" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W36" t="inlineStr">
-        <is>
-          <t>Näs</t>
-        </is>
-      </c>
-      <c r="Y36" t="inlineStr">
-        <is>
-          <t>2026-07-26</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>15:38</t>
-        </is>
-      </c>
-      <c r="AA36" t="inlineStr">
-        <is>
-          <t>2026-07-26</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>15:38</t>
-        </is>
-      </c>
-      <c r="AD36" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE36" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG36" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT36" t="inlineStr"/>
-      <c r="AW36" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX36" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY36" t="inlineStr"/>
-      <c r="AZ36" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135593870</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="n">
-        <v>135593880</v>
-      </c>
-      <c r="B37" t="n">
-        <v>78453</v>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E37" t="n">
-        <v>228579</v>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>Liten svartspik</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>Chaenothecopsis nana</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>A 28104-2026, Jmt</t>
-        </is>
-      </c>
-      <c r="Q37" t="n">
-        <v>479188</v>
-      </c>
-      <c r="R37" t="n">
-        <v>6991204</v>
-      </c>
-      <c r="S37" t="n">
-        <v>5</v>
-      </c>
-      <c r="T37" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U37" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V37" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W37" t="inlineStr">
-        <is>
-          <t>Näs</t>
-        </is>
-      </c>
-      <c r="Y37" t="inlineStr">
-        <is>
-          <t>2026-07-26</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>16:26</t>
-        </is>
-      </c>
-      <c r="AA37" t="inlineStr">
-        <is>
-          <t>2026-07-26</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>16:26</t>
-        </is>
-      </c>
-      <c r="AD37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT37" t="inlineStr"/>
-      <c r="AW37" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX37" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY37" t="inlineStr"/>
-      <c r="AZ37" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135593880</t>
         </is>
@@ -4867,9 +4516,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 28104-2026 artfynd.xlsx
+++ b/artfynd/A 28104-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ34"/>
+  <dimension ref="A1:AZ37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2263,10 +2263,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>135593878</v>
+        <v>135593860</v>
       </c>
       <c r="B16" t="n">
-        <v>58143</v>
+        <v>57982</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2274,50 +2274,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>A 28104-2026, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>479226</v>
+        <v>479454</v>
       </c>
       <c r="R16" t="n">
-        <v>6991173</v>
+        <v>6991460</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2349,7 +2333,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2359,7 +2343,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>14:19</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre spår</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2385,16 +2374,16 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135593878</t>
+          <t>https://artportalen.se/Sighting/135593860</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>135593882</v>
+        <v>135593861</v>
       </c>
       <c r="B17" t="n">
-        <v>58143</v>
+        <v>57982</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2402,53 +2391,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>A 28104-2026, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>479269</v>
+        <v>479449</v>
       </c>
       <c r="R17" t="n">
-        <v>6991246</v>
+        <v>6991399</v>
       </c>
       <c r="S17" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2477,7 +2450,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2487,7 +2460,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>14:26</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2513,38 +2491,38 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135593882</t>
+          <t>https://artportalen.se/Sighting/135593861</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>135593865</v>
+        <v>135593877</v>
       </c>
       <c r="B18" t="n">
-        <v>99212</v>
+        <v>57982</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2554,10 +2532,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>479382</v>
+        <v>479282</v>
       </c>
       <c r="R18" t="n">
-        <v>6991189</v>
+        <v>6991184</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2589,7 +2567,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2599,7 +2577,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>16:09</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2625,51 +2608,67 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135593865</t>
+          <t>https://artportalen.se/Sighting/135593877</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>135593892</v>
+        <v>135593878</v>
       </c>
       <c r="B19" t="n">
-        <v>99212</v>
+        <v>58143</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>219790</v>
+        <v>103021</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>A 28104-2026, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>479323</v>
+        <v>479226</v>
       </c>
       <c r="R19" t="n">
-        <v>6991354</v>
+        <v>6991173</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2701,7 +2700,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2711,7 +2710,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2737,54 +2736,70 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135593892</t>
+          <t>https://artportalen.se/Sighting/135593878</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>135593867</v>
+        <v>135593882</v>
       </c>
       <c r="B20" t="n">
-        <v>99295</v>
+        <v>58143</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>A 28104-2026, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>479392</v>
+        <v>479269</v>
       </c>
       <c r="R20" t="n">
-        <v>6991092</v>
+        <v>6991246</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2813,7 +2828,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2823,12 +2838,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:25</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Räknat till 25 plantor utspritt</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2854,38 +2864,38 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135593867</t>
+          <t>https://artportalen.se/Sighting/135593882</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>135593868</v>
+        <v>135593865</v>
       </c>
       <c r="B21" t="n">
-        <v>99295</v>
+        <v>99212</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2895,10 +2905,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>479398</v>
+        <v>479382</v>
       </c>
       <c r="R21" t="n">
-        <v>6991100</v>
+        <v>6991189</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2930,7 +2940,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2940,12 +2950,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:29</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Räknat till 11 plantor utspridda</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2971,38 +2976,38 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135593868</t>
+          <t>https://artportalen.se/Sighting/135593865</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>135593869</v>
+        <v>135593892</v>
       </c>
       <c r="B22" t="n">
-        <v>99295</v>
+        <v>99212</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3012,10 +3017,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>479399</v>
+        <v>479323</v>
       </c>
       <c r="R22" t="n">
-        <v>6991106</v>
+        <v>6991354</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3047,7 +3052,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3057,12 +3062,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:34</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>5 plantor</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3088,13 +3088,13 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135593869</t>
+          <t>https://artportalen.se/Sighting/135593892</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>135593872</v>
+        <v>135593867</v>
       </c>
       <c r="B23" t="n">
         <v>99295</v>
@@ -3129,10 +3129,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>479402</v>
+        <v>479392</v>
       </c>
       <c r="R23" t="n">
-        <v>6991103</v>
+        <v>6991092</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3164,7 +3164,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3174,12 +3174,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Över 20 plantor samlat. En blomstjälk.</t>
+          <t>Räknat till 25 plantor utspritt</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3205,13 +3205,13 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135593872</t>
+          <t>https://artportalen.se/Sighting/135593867</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>135593873</v>
+        <v>135593868</v>
       </c>
       <c r="B24" t="n">
         <v>99295</v>
@@ -3246,10 +3246,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>479406</v>
+        <v>479398</v>
       </c>
       <c r="R24" t="n">
-        <v>6991091</v>
+        <v>6991100</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3281,7 +3281,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3291,12 +3291,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Räknat till 5 utspridda plantor</t>
+          <t>Räknat till 11 plantor utspridda</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3322,13 +3322,13 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135593873</t>
+          <t>https://artportalen.se/Sighting/135593868</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>135593874</v>
+        <v>135593869</v>
       </c>
       <c r="B25" t="n">
         <v>99295</v>
@@ -3363,13 +3363,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>479382</v>
+        <v>479399</v>
       </c>
       <c r="R25" t="n">
-        <v>6991087</v>
+        <v>6991106</v>
       </c>
       <c r="S25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3398,7 +3398,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3408,12 +3408,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>3 plantor</t>
+          <t>5 plantor</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3439,13 +3439,13 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135593874</t>
+          <t>https://artportalen.se/Sighting/135593869</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>135593887</v>
+        <v>135593872</v>
       </c>
       <c r="B26" t="n">
         <v>99295</v>
@@ -3474,21 +3474,16 @@
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>A 28104-2026, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>479354</v>
+        <v>479402</v>
       </c>
       <c r="R26" t="n">
-        <v>6991311</v>
+        <v>6991103</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3520,7 +3515,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3530,12 +3525,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ca 15 funna plantor</t>
+          <t>Över 20 plantor samlat. En blomstjälk.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3561,13 +3556,13 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135593887</t>
+          <t>https://artportalen.se/Sighting/135593872</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>135593891</v>
+        <v>135593873</v>
       </c>
       <c r="B27" t="n">
         <v>99295</v>
@@ -3602,10 +3597,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>479329</v>
+        <v>479406</v>
       </c>
       <c r="R27" t="n">
-        <v>6991351</v>
+        <v>6991091</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3637,7 +3632,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3647,12 +3642,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Över 30 funna plantor, ganska samlat</t>
+          <t>Räknat till 5 utspridda plantor</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3678,13 +3673,13 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135593891</t>
+          <t>https://artportalen.se/Sighting/135593873</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>135593893</v>
+        <v>135593874</v>
       </c>
       <c r="B28" t="n">
         <v>99295</v>
@@ -3719,13 +3714,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>479325</v>
+        <v>479382</v>
       </c>
       <c r="R28" t="n">
-        <v>6991383</v>
+        <v>6991087</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3754,7 +3749,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3764,12 +3759,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Småplantor, över 30 st samlat</t>
+          <t>3 plantor</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3795,13 +3790,13 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135593893</t>
+          <t>https://artportalen.se/Sighting/135593874</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>135593894</v>
+        <v>135593887</v>
       </c>
       <c r="B29" t="n">
         <v>99295</v>
@@ -3830,16 +3825,21 @@
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>A 28104-2026, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>479281</v>
+        <v>479354</v>
       </c>
       <c r="R29" t="n">
-        <v>6991365</v>
+        <v>6991311</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3861,7 +3861,7 @@
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>Sunne</t>
+          <t>Näs</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
@@ -3871,7 +3871,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3881,12 +3881,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ca 10 plantor utspridda</t>
+          <t>Ca 15 funna plantor</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3912,13 +3912,13 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135593894</t>
+          <t>https://artportalen.se/Sighting/135593887</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>135593896</v>
+        <v>135593891</v>
       </c>
       <c r="B30" t="n">
         <v>99295</v>
@@ -3953,10 +3953,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>479220</v>
+        <v>479329</v>
       </c>
       <c r="R30" t="n">
-        <v>6991333</v>
+        <v>6991351</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>Sunne</t>
+          <t>Näs</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
@@ -3988,7 +3988,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3998,12 +3998,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>3 st plantor</t>
+          <t>Över 30 funna plantor, ganska samlat</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4029,38 +4029,38 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135593896</t>
+          <t>https://artportalen.se/Sighting/135593891</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>135593859</v>
+        <v>135593893</v>
       </c>
       <c r="B31" t="n">
-        <v>78453</v>
+        <v>99295</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>228579</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4070,10 +4070,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>479428</v>
+        <v>479325</v>
       </c>
       <c r="R31" t="n">
-        <v>6991450</v>
+        <v>6991383</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4105,7 +4105,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4115,7 +4115,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>17:16</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Småplantor, över 30 st samlat</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4141,38 +4146,38 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135593859</t>
+          <t>https://artportalen.se/Sighting/135593893</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>135593862</v>
+        <v>135593894</v>
       </c>
       <c r="B32" t="n">
-        <v>78453</v>
+        <v>99295</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>228579</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4182,10 +4187,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>479453</v>
+        <v>479281</v>
       </c>
       <c r="R32" t="n">
-        <v>6991398</v>
+        <v>6991365</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4207,7 +4212,7 @@
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>Näs</t>
+          <t>Sunne</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
@@ -4217,7 +4222,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4227,7 +4232,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>17:23</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ca 10 plantor utspridda</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4253,38 +4263,38 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135593862</t>
+          <t>https://artportalen.se/Sighting/135593894</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>135593870</v>
+        <v>135593896</v>
       </c>
       <c r="B33" t="n">
-        <v>78453</v>
+        <v>99295</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>228579</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4294,10 +4304,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>479402</v>
+        <v>479220</v>
       </c>
       <c r="R33" t="n">
-        <v>6991104</v>
+        <v>6991333</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4319,7 +4329,7 @@
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>Näs</t>
+          <t>Sunne</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr">
@@ -4329,7 +4339,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4339,7 +4349,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>17:32</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>3 st plantor</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4365,13 +4380,13 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135593870</t>
+          <t>https://artportalen.se/Sighting/135593896</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>135593880</v>
+        <v>135593859</v>
       </c>
       <c r="B34" t="n">
         <v>78453</v>
@@ -4406,10 +4421,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>479188</v>
+        <v>479428</v>
       </c>
       <c r="R34" t="n">
-        <v>6991204</v>
+        <v>6991450</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4441,7 +4456,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4451,7 +4466,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4476,6 +4491,342 @@
       </c>
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135593859</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>135593862</v>
+      </c>
+      <c r="B35" t="n">
+        <v>78453</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>228579</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Liten svartspik</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis nana</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>A 28104-2026, Jmt</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>479453</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6991398</v>
+      </c>
+      <c r="S35" t="n">
+        <v>5</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Näs</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>14:32</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>14:32</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135593862</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>135593870</v>
+      </c>
+      <c r="B36" t="n">
+        <v>78453</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>228579</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Liten svartspik</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis nana</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>A 28104-2026, Jmt</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>479402</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6991104</v>
+      </c>
+      <c r="S36" t="n">
+        <v>5</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Näs</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>15:38</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>15:38</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135593870</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>135593880</v>
+      </c>
+      <c r="B37" t="n">
+        <v>78453</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>228579</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Liten svartspik</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis nana</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>A 28104-2026, Jmt</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>479188</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6991204</v>
+      </c>
+      <c r="S37" t="n">
+        <v>5</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Näs</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>16:26</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>16:26</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135593880</t>
         </is>
@@ -4516,6 +4867,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 28104-2026 artfynd.xlsx
+++ b/artfynd/A 28104-2026 artfynd.xlsx
@@ -2266,7 +2266,7 @@
         <v>135593860</v>
       </c>
       <c r="B16" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2383,7 +2383,7 @@
         <v>135593861</v>
       </c>
       <c r="B17" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2500,7 +2500,7 @@
         <v>135593877</v>
       </c>
       <c r="B18" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 28104-2026 artfynd.xlsx
+++ b/artfynd/A 28104-2026 artfynd.xlsx
@@ -2266,7 +2266,7 @@
         <v>135593860</v>
       </c>
       <c r="B16" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2383,7 +2383,7 @@
         <v>135593861</v>
       </c>
       <c r="B17" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2500,7 +2500,7 @@
         <v>135593877</v>
       </c>
       <c r="B18" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 28104-2026 artfynd.xlsx
+++ b/artfynd/A 28104-2026 artfynd.xlsx
@@ -2266,7 +2266,7 @@
         <v>135593860</v>
       </c>
       <c r="B16" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2383,7 +2383,7 @@
         <v>135593861</v>
       </c>
       <c r="B17" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2500,7 +2500,7 @@
         <v>135593877</v>
       </c>
       <c r="B18" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 28104-2026 artfynd.xlsx
+++ b/artfynd/A 28104-2026 artfynd.xlsx
@@ -2266,7 +2266,7 @@
         <v>135593860</v>
       </c>
       <c r="B16" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2383,7 +2383,7 @@
         <v>135593861</v>
       </c>
       <c r="B17" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2500,7 +2500,7 @@
         <v>135593877</v>
       </c>
       <c r="B18" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 28104-2026 artfynd.xlsx
+++ b/artfynd/A 28104-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ37"/>
+  <dimension ref="A1:AZ34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2263,10 +2263,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>135593860</v>
+        <v>135593878</v>
       </c>
       <c r="B16" t="n">
-        <v>57993</v>
+        <v>58143</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2274,34 +2274,50 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>A 28104-2026, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>479454</v>
+        <v>479226</v>
       </c>
       <c r="R16" t="n">
-        <v>6991460</v>
+        <v>6991173</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2333,7 +2349,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2343,12 +2359,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:19</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre spår</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2374,16 +2385,16 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135593860</t>
+          <t>https://artportalen.se/Sighting/135593878</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>135593861</v>
+        <v>135593882</v>
       </c>
       <c r="B17" t="n">
-        <v>57993</v>
+        <v>58143</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2391,37 +2402,53 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>A 28104-2026, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>479449</v>
+        <v>479269</v>
       </c>
       <c r="R17" t="n">
-        <v>6991399</v>
+        <v>6991246</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2450,7 +2477,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2460,12 +2487,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:26</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2491,38 +2513,38 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135593861</t>
+          <t>https://artportalen.se/Sighting/135593882</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>135593877</v>
+        <v>135593865</v>
       </c>
       <c r="B18" t="n">
-        <v>57993</v>
+        <v>99212</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>219790</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2532,10 +2554,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>479282</v>
+        <v>479382</v>
       </c>
       <c r="R18" t="n">
-        <v>6991184</v>
+        <v>6991189</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2567,7 +2589,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2577,12 +2599,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16:09</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2608,67 +2625,51 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135593877</t>
+          <t>https://artportalen.se/Sighting/135593865</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>135593878</v>
+        <v>135593892</v>
       </c>
       <c r="B19" t="n">
-        <v>58143</v>
+        <v>99212</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103021</v>
+        <v>219790</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>A 28104-2026, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>479226</v>
+        <v>479323</v>
       </c>
       <c r="R19" t="n">
-        <v>6991173</v>
+        <v>6991354</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2700,7 +2701,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2710,7 +2711,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2736,70 +2737,54 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135593878</t>
+          <t>https://artportalen.se/Sighting/135593892</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>135593882</v>
+        <v>135593867</v>
       </c>
       <c r="B20" t="n">
-        <v>58143</v>
+        <v>99295</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>A 28104-2026, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>479269</v>
+        <v>479392</v>
       </c>
       <c r="R20" t="n">
-        <v>6991246</v>
+        <v>6991092</v>
       </c>
       <c r="S20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2828,7 +2813,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2838,7 +2823,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Räknat till 25 plantor utspritt</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2864,38 +2854,38 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135593882</t>
+          <t>https://artportalen.se/Sighting/135593867</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>135593865</v>
+        <v>135593868</v>
       </c>
       <c r="B21" t="n">
-        <v>99212</v>
+        <v>99295</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2905,10 +2895,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>479382</v>
+        <v>479398</v>
       </c>
       <c r="R21" t="n">
-        <v>6991189</v>
+        <v>6991100</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2940,7 +2930,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2950,7 +2940,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>15:29</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Räknat till 11 plantor utspridda</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2976,38 +2971,38 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135593865</t>
+          <t>https://artportalen.se/Sighting/135593868</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>135593892</v>
+        <v>135593869</v>
       </c>
       <c r="B22" t="n">
-        <v>99212</v>
+        <v>99295</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3017,10 +3012,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>479323</v>
+        <v>479399</v>
       </c>
       <c r="R22" t="n">
-        <v>6991354</v>
+        <v>6991106</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3052,7 +3047,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3062,7 +3057,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>15:34</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>5 plantor</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3088,13 +3088,13 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135593892</t>
+          <t>https://artportalen.se/Sighting/135593869</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>135593867</v>
+        <v>135593872</v>
       </c>
       <c r="B23" t="n">
         <v>99295</v>
@@ -3129,10 +3129,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>479392</v>
+        <v>479402</v>
       </c>
       <c r="R23" t="n">
-        <v>6991092</v>
+        <v>6991103</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3164,7 +3164,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3174,12 +3174,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Räknat till 25 plantor utspritt</t>
+          <t>Över 20 plantor samlat. En blomstjälk.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3205,13 +3205,13 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135593867</t>
+          <t>https://artportalen.se/Sighting/135593872</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>135593868</v>
+        <v>135593873</v>
       </c>
       <c r="B24" t="n">
         <v>99295</v>
@@ -3246,10 +3246,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>479398</v>
+        <v>479406</v>
       </c>
       <c r="R24" t="n">
-        <v>6991100</v>
+        <v>6991091</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3281,7 +3281,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3291,12 +3291,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Räknat till 11 plantor utspridda</t>
+          <t>Räknat till 5 utspridda plantor</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3322,13 +3322,13 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135593868</t>
+          <t>https://artportalen.se/Sighting/135593873</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>135593869</v>
+        <v>135593874</v>
       </c>
       <c r="B25" t="n">
         <v>99295</v>
@@ -3363,13 +3363,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>479399</v>
+        <v>479382</v>
       </c>
       <c r="R25" t="n">
-        <v>6991106</v>
+        <v>6991087</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3398,7 +3398,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3408,12 +3408,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>5 plantor</t>
+          <t>3 plantor</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3439,13 +3439,13 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135593869</t>
+          <t>https://artportalen.se/Sighting/135593874</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>135593872</v>
+        <v>135593887</v>
       </c>
       <c r="B26" t="n">
         <v>99295</v>
@@ -3474,16 +3474,21 @@
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>A 28104-2026, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>479402</v>
+        <v>479354</v>
       </c>
       <c r="R26" t="n">
-        <v>6991103</v>
+        <v>6991311</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3515,7 +3520,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3525,12 +3530,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Över 20 plantor samlat. En blomstjälk.</t>
+          <t>Ca 15 funna plantor</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3556,13 +3561,13 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135593872</t>
+          <t>https://artportalen.se/Sighting/135593887</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>135593873</v>
+        <v>135593891</v>
       </c>
       <c r="B27" t="n">
         <v>99295</v>
@@ -3597,10 +3602,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>479406</v>
+        <v>479329</v>
       </c>
       <c r="R27" t="n">
-        <v>6991091</v>
+        <v>6991351</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3632,7 +3637,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3642,12 +3647,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Räknat till 5 utspridda plantor</t>
+          <t>Över 30 funna plantor, ganska samlat</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3673,13 +3678,13 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135593873</t>
+          <t>https://artportalen.se/Sighting/135593891</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>135593874</v>
+        <v>135593893</v>
       </c>
       <c r="B28" t="n">
         <v>99295</v>
@@ -3714,13 +3719,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>479382</v>
+        <v>479325</v>
       </c>
       <c r="R28" t="n">
-        <v>6991087</v>
+        <v>6991383</v>
       </c>
       <c r="S28" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3749,7 +3754,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3759,12 +3764,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>3 plantor</t>
+          <t>Småplantor, över 30 st samlat</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3790,13 +3795,13 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135593874</t>
+          <t>https://artportalen.se/Sighting/135593893</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>135593887</v>
+        <v>135593894</v>
       </c>
       <c r="B29" t="n">
         <v>99295</v>
@@ -3825,21 +3830,16 @@
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>A 28104-2026, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>479354</v>
+        <v>479281</v>
       </c>
       <c r="R29" t="n">
-        <v>6991311</v>
+        <v>6991365</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3861,7 +3861,7 @@
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>Näs</t>
+          <t>Sunne</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
@@ -3871,7 +3871,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3881,12 +3881,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ca 15 funna plantor</t>
+          <t>Ca 10 plantor utspridda</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3912,13 +3912,13 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135593887</t>
+          <t>https://artportalen.se/Sighting/135593894</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>135593891</v>
+        <v>135593896</v>
       </c>
       <c r="B30" t="n">
         <v>99295</v>
@@ -3953,10 +3953,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>479329</v>
+        <v>479220</v>
       </c>
       <c r="R30" t="n">
-        <v>6991351</v>
+        <v>6991333</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>Näs</t>
+          <t>Sunne</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
@@ -3988,7 +3988,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3998,12 +3998,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Över 30 funna plantor, ganska samlat</t>
+          <t>3 st plantor</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4029,38 +4029,38 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135593891</t>
+          <t>https://artportalen.se/Sighting/135593896</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>135593893</v>
+        <v>135593859</v>
       </c>
       <c r="B31" t="n">
-        <v>99295</v>
+        <v>78453</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>228579</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4070,10 +4070,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>479325</v>
+        <v>479428</v>
       </c>
       <c r="R31" t="n">
-        <v>6991383</v>
+        <v>6991450</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4105,7 +4105,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4115,12 +4115,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>17:16</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Småplantor, över 30 st samlat</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4146,38 +4141,38 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135593893</t>
+          <t>https://artportalen.se/Sighting/135593859</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>135593894</v>
+        <v>135593862</v>
       </c>
       <c r="B32" t="n">
-        <v>99295</v>
+        <v>78453</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>228579</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4187,10 +4182,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>479281</v>
+        <v>479453</v>
       </c>
       <c r="R32" t="n">
-        <v>6991365</v>
+        <v>6991398</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4212,7 +4207,7 @@
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>Sunne</t>
+          <t>Näs</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
@@ -4222,7 +4217,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4232,12 +4227,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>17:23</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Ca 10 plantor utspridda</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4263,38 +4253,38 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135593894</t>
+          <t>https://artportalen.se/Sighting/135593862</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>135593896</v>
+        <v>135593870</v>
       </c>
       <c r="B33" t="n">
-        <v>99295</v>
+        <v>78453</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>228579</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4304,10 +4294,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>479220</v>
+        <v>479402</v>
       </c>
       <c r="R33" t="n">
-        <v>6991333</v>
+        <v>6991104</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4329,7 +4319,7 @@
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>Sunne</t>
+          <t>Näs</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr">
@@ -4339,7 +4329,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4349,12 +4339,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>17:32</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>3 st plantor</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4380,13 +4365,13 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135593896</t>
+          <t>https://artportalen.se/Sighting/135593870</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>135593859</v>
+        <v>135593880</v>
       </c>
       <c r="B34" t="n">
         <v>78453</v>
@@ -4421,10 +4406,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>479428</v>
+        <v>479188</v>
       </c>
       <c r="R34" t="n">
-        <v>6991450</v>
+        <v>6991204</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4456,7 +4441,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4466,7 +4451,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4491,342 +4476,6 @@
       </c>
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135593859</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="n">
-        <v>135593862</v>
-      </c>
-      <c r="B35" t="n">
-        <v>78453</v>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E35" t="n">
-        <v>228579</v>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>Liten svartspik</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>Chaenothecopsis nana</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>A 28104-2026, Jmt</t>
-        </is>
-      </c>
-      <c r="Q35" t="n">
-        <v>479453</v>
-      </c>
-      <c r="R35" t="n">
-        <v>6991398</v>
-      </c>
-      <c r="S35" t="n">
-        <v>5</v>
-      </c>
-      <c r="T35" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U35" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V35" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W35" t="inlineStr">
-        <is>
-          <t>Näs</t>
-        </is>
-      </c>
-      <c r="Y35" t="inlineStr">
-        <is>
-          <t>2026-07-26</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>14:32</t>
-        </is>
-      </c>
-      <c r="AA35" t="inlineStr">
-        <is>
-          <t>2026-07-26</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>14:32</t>
-        </is>
-      </c>
-      <c r="AD35" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE35" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG35" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT35" t="inlineStr"/>
-      <c r="AW35" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX35" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY35" t="inlineStr"/>
-      <c r="AZ35" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135593862</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="n">
-        <v>135593870</v>
-      </c>
-      <c r="B36" t="n">
-        <v>78453</v>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E36" t="n">
-        <v>228579</v>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>Liten svartspik</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>Chaenothecopsis nana</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>A 28104-2026, Jmt</t>
-        </is>
-      </c>
-      <c r="Q36" t="n">
-        <v>479402</v>
-      </c>
-      <c r="R36" t="n">
-        <v>6991104</v>
-      </c>
-      <c r="S36" t="n">
-        <v>5</v>
-      </c>
-      <c r="T36" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U36" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V36" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W36" t="inlineStr">
-        <is>
-          <t>Näs</t>
-        </is>
-      </c>
-      <c r="Y36" t="inlineStr">
-        <is>
-          <t>2026-07-26</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>15:38</t>
-        </is>
-      </c>
-      <c r="AA36" t="inlineStr">
-        <is>
-          <t>2026-07-26</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>15:38</t>
-        </is>
-      </c>
-      <c r="AD36" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE36" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG36" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT36" t="inlineStr"/>
-      <c r="AW36" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX36" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY36" t="inlineStr"/>
-      <c r="AZ36" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135593870</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="n">
-        <v>135593880</v>
-      </c>
-      <c r="B37" t="n">
-        <v>78453</v>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E37" t="n">
-        <v>228579</v>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>Liten svartspik</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>Chaenothecopsis nana</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>A 28104-2026, Jmt</t>
-        </is>
-      </c>
-      <c r="Q37" t="n">
-        <v>479188</v>
-      </c>
-      <c r="R37" t="n">
-        <v>6991204</v>
-      </c>
-      <c r="S37" t="n">
-        <v>5</v>
-      </c>
-      <c r="T37" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U37" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V37" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W37" t="inlineStr">
-        <is>
-          <t>Näs</t>
-        </is>
-      </c>
-      <c r="Y37" t="inlineStr">
-        <is>
-          <t>2026-07-26</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>16:26</t>
-        </is>
-      </c>
-      <c r="AA37" t="inlineStr">
-        <is>
-          <t>2026-07-26</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>16:26</t>
-        </is>
-      </c>
-      <c r="AD37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT37" t="inlineStr"/>
-      <c r="AW37" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX37" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY37" t="inlineStr"/>
-      <c r="AZ37" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135593880</t>
         </is>
@@ -4867,9 +4516,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 28104-2026 artfynd.xlsx
+++ b/artfynd/A 28104-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ34"/>
+  <dimension ref="A1:AZ37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2263,10 +2263,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>135593878</v>
+        <v>135593860</v>
       </c>
       <c r="B16" t="n">
-        <v>58143</v>
+        <v>58006</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2274,50 +2274,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>A 28104-2026, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>479226</v>
+        <v>479454</v>
       </c>
       <c r="R16" t="n">
-        <v>6991173</v>
+        <v>6991460</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2349,7 +2333,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2359,7 +2343,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>14:19</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre spår</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2385,16 +2374,16 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135593878</t>
+          <t>https://artportalen.se/Sighting/135593860</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>135593882</v>
+        <v>135593861</v>
       </c>
       <c r="B17" t="n">
-        <v>58143</v>
+        <v>58006</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2402,53 +2391,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>A 28104-2026, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>479269</v>
+        <v>479449</v>
       </c>
       <c r="R17" t="n">
-        <v>6991246</v>
+        <v>6991399</v>
       </c>
       <c r="S17" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2477,7 +2450,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2487,7 +2460,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>14:26</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2513,38 +2491,38 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135593882</t>
+          <t>https://artportalen.se/Sighting/135593861</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>135593865</v>
+        <v>135593877</v>
       </c>
       <c r="B18" t="n">
-        <v>99212</v>
+        <v>58006</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2554,10 +2532,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>479382</v>
+        <v>479282</v>
       </c>
       <c r="R18" t="n">
-        <v>6991189</v>
+        <v>6991184</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2589,7 +2567,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2599,7 +2577,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>16:09</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2625,51 +2608,67 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135593865</t>
+          <t>https://artportalen.se/Sighting/135593877</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>135593892</v>
+        <v>135593878</v>
       </c>
       <c r="B19" t="n">
-        <v>99212</v>
+        <v>58143</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>219790</v>
+        <v>103021</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>A 28104-2026, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>479323</v>
+        <v>479226</v>
       </c>
       <c r="R19" t="n">
-        <v>6991354</v>
+        <v>6991173</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2701,7 +2700,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2711,7 +2710,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2737,54 +2736,70 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135593892</t>
+          <t>https://artportalen.se/Sighting/135593878</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>135593867</v>
+        <v>135593882</v>
       </c>
       <c r="B20" t="n">
-        <v>99295</v>
+        <v>58143</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>A 28104-2026, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>479392</v>
+        <v>479269</v>
       </c>
       <c r="R20" t="n">
-        <v>6991092</v>
+        <v>6991246</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2813,7 +2828,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2823,12 +2838,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:25</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Räknat till 25 plantor utspritt</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2854,38 +2864,38 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135593867</t>
+          <t>https://artportalen.se/Sighting/135593882</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>135593868</v>
+        <v>135593865</v>
       </c>
       <c r="B21" t="n">
-        <v>99295</v>
+        <v>99212</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2895,10 +2905,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>479398</v>
+        <v>479382</v>
       </c>
       <c r="R21" t="n">
-        <v>6991100</v>
+        <v>6991189</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2930,7 +2940,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2940,12 +2950,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:29</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Räknat till 11 plantor utspridda</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2971,38 +2976,38 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135593868</t>
+          <t>https://artportalen.se/Sighting/135593865</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>135593869</v>
+        <v>135593892</v>
       </c>
       <c r="B22" t="n">
-        <v>99295</v>
+        <v>99212</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3012,10 +3017,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>479399</v>
+        <v>479323</v>
       </c>
       <c r="R22" t="n">
-        <v>6991106</v>
+        <v>6991354</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3047,7 +3052,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3057,12 +3062,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:34</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>5 plantor</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3088,13 +3088,13 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135593869</t>
+          <t>https://artportalen.se/Sighting/135593892</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>135593872</v>
+        <v>135593867</v>
       </c>
       <c r="B23" t="n">
         <v>99295</v>
@@ -3129,10 +3129,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>479402</v>
+        <v>479392</v>
       </c>
       <c r="R23" t="n">
-        <v>6991103</v>
+        <v>6991092</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3164,7 +3164,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3174,12 +3174,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Över 20 plantor samlat. En blomstjälk.</t>
+          <t>Räknat till 25 plantor utspritt</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3205,13 +3205,13 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135593872</t>
+          <t>https://artportalen.se/Sighting/135593867</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>135593873</v>
+        <v>135593868</v>
       </c>
       <c r="B24" t="n">
         <v>99295</v>
@@ -3246,10 +3246,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>479406</v>
+        <v>479398</v>
       </c>
       <c r="R24" t="n">
-        <v>6991091</v>
+        <v>6991100</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3281,7 +3281,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3291,12 +3291,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Räknat till 5 utspridda plantor</t>
+          <t>Räknat till 11 plantor utspridda</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3322,13 +3322,13 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135593873</t>
+          <t>https://artportalen.se/Sighting/135593868</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>135593874</v>
+        <v>135593869</v>
       </c>
       <c r="B25" t="n">
         <v>99295</v>
@@ -3363,13 +3363,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>479382</v>
+        <v>479399</v>
       </c>
       <c r="R25" t="n">
-        <v>6991087</v>
+        <v>6991106</v>
       </c>
       <c r="S25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3398,7 +3398,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3408,12 +3408,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>3 plantor</t>
+          <t>5 plantor</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3439,13 +3439,13 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135593874</t>
+          <t>https://artportalen.se/Sighting/135593869</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>135593887</v>
+        <v>135593872</v>
       </c>
       <c r="B26" t="n">
         <v>99295</v>
@@ -3474,21 +3474,16 @@
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>A 28104-2026, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>479354</v>
+        <v>479402</v>
       </c>
       <c r="R26" t="n">
-        <v>6991311</v>
+        <v>6991103</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3520,7 +3515,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3530,12 +3525,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ca 15 funna plantor</t>
+          <t>Över 20 plantor samlat. En blomstjälk.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3561,13 +3556,13 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135593887</t>
+          <t>https://artportalen.se/Sighting/135593872</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>135593891</v>
+        <v>135593873</v>
       </c>
       <c r="B27" t="n">
         <v>99295</v>
@@ -3602,10 +3597,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>479329</v>
+        <v>479406</v>
       </c>
       <c r="R27" t="n">
-        <v>6991351</v>
+        <v>6991091</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3637,7 +3632,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3647,12 +3642,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Över 30 funna plantor, ganska samlat</t>
+          <t>Räknat till 5 utspridda plantor</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3678,13 +3673,13 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135593891</t>
+          <t>https://artportalen.se/Sighting/135593873</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>135593893</v>
+        <v>135593874</v>
       </c>
       <c r="B28" t="n">
         <v>99295</v>
@@ -3719,13 +3714,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>479325</v>
+        <v>479382</v>
       </c>
       <c r="R28" t="n">
-        <v>6991383</v>
+        <v>6991087</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3754,7 +3749,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3764,12 +3759,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Småplantor, över 30 st samlat</t>
+          <t>3 plantor</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3795,13 +3790,13 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135593893</t>
+          <t>https://artportalen.se/Sighting/135593874</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>135593894</v>
+        <v>135593887</v>
       </c>
       <c r="B29" t="n">
         <v>99295</v>
@@ -3830,16 +3825,21 @@
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>A 28104-2026, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>479281</v>
+        <v>479354</v>
       </c>
       <c r="R29" t="n">
-        <v>6991365</v>
+        <v>6991311</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3861,7 +3861,7 @@
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>Sunne</t>
+          <t>Näs</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
@@ -3871,7 +3871,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3881,12 +3881,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ca 10 plantor utspridda</t>
+          <t>Ca 15 funna plantor</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3912,13 +3912,13 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135593894</t>
+          <t>https://artportalen.se/Sighting/135593887</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>135593896</v>
+        <v>135593891</v>
       </c>
       <c r="B30" t="n">
         <v>99295</v>
@@ -3953,10 +3953,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>479220</v>
+        <v>479329</v>
       </c>
       <c r="R30" t="n">
-        <v>6991333</v>
+        <v>6991351</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>Sunne</t>
+          <t>Näs</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
@@ -3988,7 +3988,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3998,12 +3998,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>3 st plantor</t>
+          <t>Över 30 funna plantor, ganska samlat</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4029,38 +4029,38 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135593896</t>
+          <t>https://artportalen.se/Sighting/135593891</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>135593859</v>
+        <v>135593893</v>
       </c>
       <c r="B31" t="n">
-        <v>78453</v>
+        <v>99295</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>228579</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4070,10 +4070,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>479428</v>
+        <v>479325</v>
       </c>
       <c r="R31" t="n">
-        <v>6991450</v>
+        <v>6991383</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4105,7 +4105,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4115,7 +4115,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>17:16</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Småplantor, över 30 st samlat</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4141,38 +4146,38 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135593859</t>
+          <t>https://artportalen.se/Sighting/135593893</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>135593862</v>
+        <v>135593894</v>
       </c>
       <c r="B32" t="n">
-        <v>78453</v>
+        <v>99295</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>228579</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4182,10 +4187,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>479453</v>
+        <v>479281</v>
       </c>
       <c r="R32" t="n">
-        <v>6991398</v>
+        <v>6991365</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4207,7 +4212,7 @@
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>Näs</t>
+          <t>Sunne</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
@@ -4217,7 +4222,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4227,7 +4232,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>17:23</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ca 10 plantor utspridda</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4253,38 +4263,38 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135593862</t>
+          <t>https://artportalen.se/Sighting/135593894</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>135593870</v>
+        <v>135593896</v>
       </c>
       <c r="B33" t="n">
-        <v>78453</v>
+        <v>99295</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>228579</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4294,10 +4304,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>479402</v>
+        <v>479220</v>
       </c>
       <c r="R33" t="n">
-        <v>6991104</v>
+        <v>6991333</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4319,7 +4329,7 @@
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>Näs</t>
+          <t>Sunne</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr">
@@ -4329,7 +4339,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4339,7 +4349,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>17:32</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>3 st plantor</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4365,13 +4380,13 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135593870</t>
+          <t>https://artportalen.se/Sighting/135593896</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>135593880</v>
+        <v>135593859</v>
       </c>
       <c r="B34" t="n">
         <v>78453</v>
@@ -4406,10 +4421,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>479188</v>
+        <v>479428</v>
       </c>
       <c r="R34" t="n">
-        <v>6991204</v>
+        <v>6991450</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4441,7 +4456,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4451,7 +4466,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4476,6 +4491,342 @@
       </c>
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135593859</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>135593862</v>
+      </c>
+      <c r="B35" t="n">
+        <v>78453</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>228579</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Liten svartspik</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis nana</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>A 28104-2026, Jmt</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>479453</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6991398</v>
+      </c>
+      <c r="S35" t="n">
+        <v>5</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Näs</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>14:32</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>14:32</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135593862</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>135593870</v>
+      </c>
+      <c r="B36" t="n">
+        <v>78453</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>228579</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Liten svartspik</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis nana</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>A 28104-2026, Jmt</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>479402</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6991104</v>
+      </c>
+      <c r="S36" t="n">
+        <v>5</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Näs</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>15:38</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>15:38</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135593870</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>135593880</v>
+      </c>
+      <c r="B37" t="n">
+        <v>78453</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>228579</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Liten svartspik</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis nana</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>A 28104-2026, Jmt</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>479188</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6991204</v>
+      </c>
+      <c r="S37" t="n">
+        <v>5</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Näs</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>16:26</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>16:26</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135593880</t>
         </is>
@@ -4516,6 +4867,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
